--- a/data/releases/v2.0/china_city_entity_master_V2.0.xlsx
+++ b/data/releases/v2.0/china_city_entity_master_V2.0.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市总表" sheetId="1" r:id="Rbd6ba5aaff8f4050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市总表" sheetId="1" r:id="R6849269ba1a643d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -113,7 +113,7 @@
     <x:tableColumn id="7" name="entity_type"/>
     <x:tableColumn id="8" name="first_active_year"/>
     <x:tableColumn id="9" name="last_active_year"/>
-    <x:tableColumn id="10" name="status_in_2024"/>
+    <x:tableColumn id="10" name="status_in_2026"/>
     <x:tableColumn id="11" name="verification_status"/>
     <x:tableColumn id="12" name="name_history"/>
     <x:tableColumn id="13" name="event_count"/>
@@ -365,7 +365,7 @@
         <x:v>last_active_year</x:v>
       </x:c>
       <x:c r="J1" s="10" t="str">
-        <x:v>status_in_2024</x:v>
+        <x:v>status_in_2026</x:v>
       </x:c>
       <x:c r="K1" s="10" t="str">
         <x:v>verification_status</x:v>
@@ -406,10 +406,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J2" s="2" t="str">
         <x:v>active</x:v>
@@ -418,7 +418,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L2" s="14" t="str">
-        <x:v>2000-2024 北京市</x:v>
+        <x:v>1987-2026 北京市</x:v>
       </x:c>
       <x:c r="M2" s="15" t="str">
         <x:v>0</x:v>
@@ -449,10 +449,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J3" s="2" t="str">
         <x:v>active</x:v>
@@ -461,7 +461,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L3" s="14" t="str">
-        <x:v>2000-2024 天津市</x:v>
+        <x:v>1987-2026 天津市</x:v>
       </x:c>
       <x:c r="M3" s="15" t="str">
         <x:v>0</x:v>
@@ -492,10 +492,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J4" s="2" t="str">
         <x:v>active</x:v>
@@ -504,7 +504,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L4" s="14" t="str">
-        <x:v>2000-2024 石家庄市</x:v>
+        <x:v>1987-2026 石家庄市</x:v>
       </x:c>
       <x:c r="M4" s="15" t="str">
         <x:v>1</x:v>
@@ -535,10 +535,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J5" s="2" t="str">
         <x:v>active</x:v>
@@ -547,7 +547,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L5" s="14" t="str">
-        <x:v>2000-2024 唐山市</x:v>
+        <x:v>1987-2026 唐山市</x:v>
       </x:c>
       <x:c r="M5" s="15" t="str">
         <x:v>0</x:v>
@@ -578,10 +578,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J6" s="2" t="str">
         <x:v>active</x:v>
@@ -590,7 +590,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L6" s="14" t="str">
-        <x:v>2000-2024 秦皇岛市</x:v>
+        <x:v>1987-2026 秦皇岛市</x:v>
       </x:c>
       <x:c r="M6" s="15" t="str">
         <x:v>0</x:v>
@@ -621,10 +621,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="2" t="str">
         <x:v>active</x:v>
@@ -633,7 +633,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L7" s="14" t="str">
-        <x:v>2000-2024 邯郸市</x:v>
+        <x:v>1987-2026 邯郸市</x:v>
       </x:c>
       <x:c r="M7" s="15" t="str">
         <x:v>0</x:v>
@@ -664,10 +664,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="2" t="str">
         <x:v>active</x:v>
@@ -676,7 +676,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L8" s="14" t="str">
-        <x:v>2000-2024 邢台市</x:v>
+        <x:v>1987-2026 邢台市</x:v>
       </x:c>
       <x:c r="M8" s="15" t="str">
         <x:v>0</x:v>
@@ -707,10 +707,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="2" t="str">
         <x:v>active</x:v>
@@ -719,7 +719,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L9" s="14" t="str">
-        <x:v>2000-2024 保定市</x:v>
+        <x:v>1987-2026 保定市</x:v>
       </x:c>
       <x:c r="M9" s="15" t="str">
         <x:v>0</x:v>
@@ -750,10 +750,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H10" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="2" t="str">
         <x:v>active</x:v>
@@ -762,7 +762,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L10" s="14" t="str">
-        <x:v>2000-2024 张家口市</x:v>
+        <x:v>1987-2026 张家口市</x:v>
       </x:c>
       <x:c r="M10" s="15" t="str">
         <x:v>0</x:v>
@@ -793,10 +793,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I11" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="2" t="str">
         <x:v>active</x:v>
@@ -805,7 +805,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L11" s="14" t="str">
-        <x:v>2000-2024 承德市</x:v>
+        <x:v>1987-2026 承德市</x:v>
       </x:c>
       <x:c r="M11" s="15" t="str">
         <x:v>0</x:v>
@@ -836,10 +836,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H12" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I12" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="2" t="str">
         <x:v>active</x:v>
@@ -848,7 +848,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L12" s="14" t="str">
-        <x:v>2000-2024 沧州市</x:v>
+        <x:v>1987-2026 沧州市</x:v>
       </x:c>
       <x:c r="M12" s="15" t="str">
         <x:v>0</x:v>
@@ -879,10 +879,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H13" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I13" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="2" t="str">
         <x:v>active</x:v>
@@ -891,7 +891,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L13" s="14" t="str">
-        <x:v>2000-2024 廊坊市</x:v>
+        <x:v>1987-1987 廊坊地区; 1988-2026 廊坊市</x:v>
       </x:c>
       <x:c r="M13" s="15" t="str">
         <x:v>1</x:v>
@@ -922,10 +922,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H14" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I14" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="2" t="str">
         <x:v>active</x:v>
@@ -934,7 +934,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L14" s="14" t="str">
-        <x:v>2000-2024 衡水市</x:v>
+        <x:v>1987-1995 衡水地区; 1996-2026 衡水市</x:v>
       </x:c>
       <x:c r="M14" s="15" t="str">
         <x:v>1</x:v>
@@ -965,10 +965,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H15" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I15" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="2" t="str">
         <x:v>active</x:v>
@@ -977,7 +977,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L15" s="14" t="str">
-        <x:v>2000-2024 太原市</x:v>
+        <x:v>1987-2026 太原市</x:v>
       </x:c>
       <x:c r="M15" s="15" t="str">
         <x:v>0</x:v>
@@ -1008,10 +1008,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H16" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I16" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="2" t="str">
         <x:v>active</x:v>
@@ -1020,7 +1020,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L16" s="14" t="str">
-        <x:v>2000-2024 大同市</x:v>
+        <x:v>1987-2026 大同市</x:v>
       </x:c>
       <x:c r="M16" s="15" t="str">
         <x:v>0</x:v>
@@ -1051,10 +1051,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H17" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I17" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="2" t="str">
         <x:v>active</x:v>
@@ -1063,7 +1063,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L17" s="14" t="str">
-        <x:v>2000-2024 阳泉市</x:v>
+        <x:v>1987-2026 阳泉市</x:v>
       </x:c>
       <x:c r="M17" s="15" t="str">
         <x:v>0</x:v>
@@ -1094,10 +1094,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H18" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I18" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="2" t="str">
         <x:v>active</x:v>
@@ -1106,7 +1106,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L18" s="14" t="str">
-        <x:v>2000-2024 长治市</x:v>
+        <x:v>1987-2026 长治市</x:v>
       </x:c>
       <x:c r="M18" s="15" t="str">
         <x:v>0</x:v>
@@ -1137,10 +1137,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H19" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I19" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="2" t="str">
         <x:v>active</x:v>
@@ -1149,7 +1149,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
-        <x:v>2000-2024 晋城市</x:v>
+        <x:v>1987-2026 晋城市</x:v>
       </x:c>
       <x:c r="M19" s="15" t="str">
         <x:v>0</x:v>
@@ -1180,10 +1180,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H20" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I20" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="2" t="str">
         <x:v>active</x:v>
@@ -1192,7 +1192,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>2000-2024 朔州市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 朔州市</x:v>
       </x:c>
       <x:c r="M20" s="15" t="str">
         <x:v>1</x:v>
@@ -1223,10 +1223,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H21" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I21" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="2" t="str">
         <x:v>active</x:v>
@@ -1235,7 +1235,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>2000-2024 晋中市</x:v>
+        <x:v>1987-1998 晋中地区; 1999-2026 晋中市</x:v>
       </x:c>
       <x:c r="M21" s="15" t="str">
         <x:v>1</x:v>
@@ -1266,10 +1266,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H22" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I22" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="2" t="str">
         <x:v>active</x:v>
@@ -1278,7 +1278,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
-        <x:v>2000-2024 运城市</x:v>
+        <x:v>1987-1999 运城地区; 2000-2026 运城市</x:v>
       </x:c>
       <x:c r="M22" s="15" t="str">
         <x:v>1</x:v>
@@ -1309,10 +1309,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H23" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I23" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="2" t="str">
         <x:v>active</x:v>
@@ -1321,7 +1321,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>2000-2024 忻州市</x:v>
+        <x:v>1987-1999 忻州地区; 2000-2026 忻州市</x:v>
       </x:c>
       <x:c r="M23" s="15" t="str">
         <x:v>1</x:v>
@@ -1352,10 +1352,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H24" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I24" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="2" t="str">
         <x:v>active</x:v>
@@ -1364,7 +1364,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>2000-2024 临汾市</x:v>
+        <x:v>1987-1999 临汾地区; 2000-2026 临汾市</x:v>
       </x:c>
       <x:c r="M24" s="15" t="str">
         <x:v>1</x:v>
@@ -1395,10 +1395,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H25" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I25" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="2" t="str">
         <x:v>active</x:v>
@@ -1407,7 +1407,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>2000-2002 吕梁地区; 2003-2024 吕梁市</x:v>
+        <x:v>1987-2002 吕梁地区; 2003-2026 吕梁市</x:v>
       </x:c>
       <x:c r="M25" s="15" t="str">
         <x:v>1</x:v>
@@ -1438,10 +1438,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H26" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I26" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="2" t="str">
         <x:v>active</x:v>
@@ -1450,7 +1450,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
-        <x:v>2000-2024 呼和浩特市</x:v>
+        <x:v>1987-2026 呼和浩特市</x:v>
       </x:c>
       <x:c r="M26" s="15" t="str">
         <x:v>0</x:v>
@@ -1481,10 +1481,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H27" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I27" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="2" t="str">
         <x:v>active</x:v>
@@ -1493,7 +1493,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>2000-2024 包头市</x:v>
+        <x:v>1987-2026 包头市</x:v>
       </x:c>
       <x:c r="M27" s="15" t="str">
         <x:v>0</x:v>
@@ -1524,10 +1524,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H28" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I28" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="2" t="str">
         <x:v>active</x:v>
@@ -1536,7 +1536,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
-        <x:v>2000-2024 乌海市</x:v>
+        <x:v>1987-2026 乌海市</x:v>
       </x:c>
       <x:c r="M28" s="15" t="str">
         <x:v>0</x:v>
@@ -1567,10 +1567,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H29" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I29" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J29" s="2" t="str">
         <x:v>active</x:v>
@@ -1579,7 +1579,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L29" s="14" t="str">
-        <x:v>2000-2024 赤峰市</x:v>
+        <x:v>1987-2026 赤峰市</x:v>
       </x:c>
       <x:c r="M29" s="15" t="str">
         <x:v>0</x:v>
@@ -1610,10 +1610,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I30" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="2" t="str">
         <x:v>active</x:v>
@@ -1622,7 +1622,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L30" s="14" t="str">
-        <x:v>2000-2024 通辽市</x:v>
+        <x:v>1987-1998 哲里木盟; 1999-2026 通辽市</x:v>
       </x:c>
       <x:c r="M30" s="15" t="str">
         <x:v>1</x:v>
@@ -1653,10 +1653,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H31" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I31" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J31" s="2" t="str">
         <x:v>active</x:v>
@@ -1665,7 +1665,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L31" s="14" t="str">
-        <x:v>2000-2000 伊克昭盟; 2001-2024 鄂尔多斯市</x:v>
+        <x:v>1987-2000 伊克昭盟; 2001-2026 鄂尔多斯市</x:v>
       </x:c>
       <x:c r="M31" s="15" t="str">
         <x:v>1</x:v>
@@ -1696,10 +1696,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H32" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I32" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J32" s="2" t="str">
         <x:v>active</x:v>
@@ -1708,7 +1708,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
-        <x:v>2000-2000 呼伦贝尔盟; 2001-2024 呼伦贝尔市</x:v>
+        <x:v>1987-2000 呼伦贝尔盟; 2001-2026 呼伦贝尔市</x:v>
       </x:c>
       <x:c r="M32" s="15" t="str">
         <x:v>1</x:v>
@@ -1739,10 +1739,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H33" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I33" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J33" s="2" t="str">
         <x:v>active</x:v>
@@ -1751,7 +1751,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L33" s="14" t="str">
-        <x:v>2000-2002 巴彦淖尔盟; 2003-2024 巴彦淖尔市</x:v>
+        <x:v>1987-2002 巴彦淖尔盟; 2003-2026 巴彦淖尔市</x:v>
       </x:c>
       <x:c r="M33" s="15" t="str">
         <x:v>1</x:v>
@@ -1782,10 +1782,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H34" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I34" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J34" s="2" t="str">
         <x:v>active</x:v>
@@ -1794,7 +1794,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L34" s="14" t="str">
-        <x:v>2000-2002 乌兰察布盟; 2003-2024 乌兰察布市</x:v>
+        <x:v>1987-2002 乌兰察布盟; 2003-2026 乌兰察布市</x:v>
       </x:c>
       <x:c r="M34" s="15" t="str">
         <x:v>1</x:v>
@@ -1825,10 +1825,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H35" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I35" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J35" s="2" t="str">
         <x:v>active</x:v>
@@ -1837,7 +1837,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L35" s="14" t="str">
-        <x:v>2000-2024 兴安盟</x:v>
+        <x:v>1987-2026 兴安盟</x:v>
       </x:c>
       <x:c r="M35" s="15" t="str">
         <x:v>0</x:v>
@@ -1868,10 +1868,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H36" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I36" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J36" s="2" t="str">
         <x:v>active</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L36" s="14" t="str">
-        <x:v>2000-2024 锡林郭勒盟</x:v>
+        <x:v>1987-2026 锡林郭勒盟</x:v>
       </x:c>
       <x:c r="M36" s="15" t="str">
         <x:v>0</x:v>
@@ -1911,10 +1911,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H37" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I37" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J37" s="2" t="str">
         <x:v>active</x:v>
@@ -1923,7 +1923,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L37" s="14" t="str">
-        <x:v>2000-2024 阿拉善盟</x:v>
+        <x:v>1987-2026 阿拉善盟</x:v>
       </x:c>
       <x:c r="M37" s="15" t="str">
         <x:v>0</x:v>
@@ -1954,10 +1954,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H38" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I38" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J38" s="2" t="str">
         <x:v>active</x:v>
@@ -1966,7 +1966,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L38" s="14" t="str">
-        <x:v>2000-2024 沈阳市</x:v>
+        <x:v>1987-2026 沈阳市</x:v>
       </x:c>
       <x:c r="M38" s="15" t="str">
         <x:v>0</x:v>
@@ -1997,10 +1997,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H39" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I39" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J39" s="2" t="str">
         <x:v>active</x:v>
@@ -2009,7 +2009,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L39" s="14" t="str">
-        <x:v>2000-2024 大连市</x:v>
+        <x:v>1987-2026 大连市</x:v>
       </x:c>
       <x:c r="M39" s="15" t="str">
         <x:v>0</x:v>
@@ -2040,10 +2040,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H40" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I40" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J40" s="2" t="str">
         <x:v>active</x:v>
@@ -2052,7 +2052,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L40" s="14" t="str">
-        <x:v>2000-2024 鞍山市</x:v>
+        <x:v>1987-2026 鞍山市</x:v>
       </x:c>
       <x:c r="M40" s="15" t="str">
         <x:v>0</x:v>
@@ -2083,10 +2083,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H41" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I41" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J41" s="2" t="str">
         <x:v>active</x:v>
@@ -2095,7 +2095,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L41" s="14" t="str">
-        <x:v>2000-2024 抚顺市</x:v>
+        <x:v>1987-2026 抚顺市</x:v>
       </x:c>
       <x:c r="M41" s="15" t="str">
         <x:v>0</x:v>
@@ -2126,10 +2126,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H42" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I42" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J42" s="2" t="str">
         <x:v>active</x:v>
@@ -2138,7 +2138,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L42" s="14" t="str">
-        <x:v>2000-2024 本溪市</x:v>
+        <x:v>1987-2026 本溪市</x:v>
       </x:c>
       <x:c r="M42" s="15" t="str">
         <x:v>0</x:v>
@@ -2169,10 +2169,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H43" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I43" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J43" s="2" t="str">
         <x:v>active</x:v>
@@ -2181,7 +2181,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L43" s="14" t="str">
-        <x:v>2000-2024 丹东市</x:v>
+        <x:v>1987-2026 丹东市</x:v>
       </x:c>
       <x:c r="M43" s="15" t="str">
         <x:v>0</x:v>
@@ -2212,10 +2212,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H44" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I44" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J44" s="2" t="str">
         <x:v>active</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L44" s="14" t="str">
-        <x:v>2000-2024 锦州市</x:v>
+        <x:v>1987-2026 锦州市</x:v>
       </x:c>
       <x:c r="M44" s="15" t="str">
         <x:v>0</x:v>
@@ -2255,10 +2255,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H45" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I45" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J45" s="2" t="str">
         <x:v>active</x:v>
@@ -2267,7 +2267,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L45" s="14" t="str">
-        <x:v>2000-2024 营口市</x:v>
+        <x:v>1987-2026 营口市</x:v>
       </x:c>
       <x:c r="M45" s="15" t="str">
         <x:v>0</x:v>
@@ -2298,10 +2298,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H46" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I46" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J46" s="2" t="str">
         <x:v>active</x:v>
@@ -2310,7 +2310,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L46" s="14" t="str">
-        <x:v>2000-2024 阜新市</x:v>
+        <x:v>1987-2026 阜新市</x:v>
       </x:c>
       <x:c r="M46" s="15" t="str">
         <x:v>0</x:v>
@@ -2341,10 +2341,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H47" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I47" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J47" s="2" t="str">
         <x:v>active</x:v>
@@ -2353,7 +2353,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L47" s="14" t="str">
-        <x:v>2000-2024 辽阳市</x:v>
+        <x:v>1987-2026 辽阳市</x:v>
       </x:c>
       <x:c r="M47" s="15" t="str">
         <x:v>0</x:v>
@@ -2384,10 +2384,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H48" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I48" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J48" s="2" t="str">
         <x:v>active</x:v>
@@ -2396,7 +2396,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L48" s="14" t="str">
-        <x:v>2000-2024 盘锦市</x:v>
+        <x:v>1987-2026 盘锦市</x:v>
       </x:c>
       <x:c r="M48" s="15" t="str">
         <x:v>0</x:v>
@@ -2427,10 +2427,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H49" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I49" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J49" s="2" t="str">
         <x:v>active</x:v>
@@ -2439,7 +2439,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L49" s="14" t="str">
-        <x:v>2000-2024 铁岭市</x:v>
+        <x:v>1987-2026 铁岭市</x:v>
       </x:c>
       <x:c r="M49" s="15" t="str">
         <x:v>0</x:v>
@@ -2470,10 +2470,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H50" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I50" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J50" s="2" t="str">
         <x:v>active</x:v>
@@ -2482,7 +2482,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L50" s="14" t="str">
-        <x:v>2000-2024 朝阳市</x:v>
+        <x:v>1987-2026 朝阳市</x:v>
       </x:c>
       <x:c r="M50" s="15" t="str">
         <x:v>0</x:v>
@@ -2513,10 +2513,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H51" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I51" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J51" s="2" t="str">
         <x:v>active</x:v>
@@ -2525,7 +2525,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L51" s="14" t="str">
-        <x:v>2000-2024 葫芦岛市</x:v>
+        <x:v>1987-1993 锦西市; 1994-2026 葫芦岛市</x:v>
       </x:c>
       <x:c r="M51" s="15" t="str">
         <x:v>1</x:v>
@@ -2556,10 +2556,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H52" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I52" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J52" s="2" t="str">
         <x:v>active</x:v>
@@ -2568,7 +2568,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L52" s="14" t="str">
-        <x:v>2000-2024 长春市</x:v>
+        <x:v>1987-2026 长春市</x:v>
       </x:c>
       <x:c r="M52" s="15" t="str">
         <x:v>0</x:v>
@@ -2599,10 +2599,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H53" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I53" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J53" s="2" t="str">
         <x:v>active</x:v>
@@ -2611,7 +2611,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L53" s="14" t="str">
-        <x:v>2000-2024 吉林市</x:v>
+        <x:v>1987-2026 吉林市</x:v>
       </x:c>
       <x:c r="M53" s="15" t="str">
         <x:v>0</x:v>
@@ -2642,10 +2642,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H54" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I54" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J54" s="2" t="str">
         <x:v>active</x:v>
@@ -2654,7 +2654,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L54" s="14" t="str">
-        <x:v>2000-2024 四平市</x:v>
+        <x:v>1987-2026 四平市</x:v>
       </x:c>
       <x:c r="M54" s="15" t="str">
         <x:v>0</x:v>
@@ -2685,10 +2685,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H55" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I55" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J55" s="2" t="str">
         <x:v>active</x:v>
@@ -2697,7 +2697,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L55" s="14" t="str">
-        <x:v>2000-2024 辽源市</x:v>
+        <x:v>1987-2026 辽源市</x:v>
       </x:c>
       <x:c r="M55" s="15" t="str">
         <x:v>0</x:v>
@@ -2728,10 +2728,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H56" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I56" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J56" s="2" t="str">
         <x:v>active</x:v>
@@ -2740,7 +2740,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L56" s="14" t="str">
-        <x:v>2000-2024 通化市</x:v>
+        <x:v>1987-2026 通化市</x:v>
       </x:c>
       <x:c r="M56" s="15" t="str">
         <x:v>0</x:v>
@@ -2771,10 +2771,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H57" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I57" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J57" s="2" t="str">
         <x:v>active</x:v>
@@ -2783,7 +2783,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L57" s="14" t="str">
-        <x:v>2000-2024 白山市</x:v>
+        <x:v>1987-1993 浑江市; 1994-2026 白山市</x:v>
       </x:c>
       <x:c r="M57" s="15" t="str">
         <x:v>1</x:v>
@@ -2814,10 +2814,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H58" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1992</x:v>
       </x:c>
       <x:c r="I58" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J58" s="2" t="str">
         <x:v>active</x:v>
@@ -2826,7 +2826,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L58" s="14" t="str">
-        <x:v>2000-2024 松原市</x:v>
+        <x:v>1987-1991 [not_established]; 1992-2026 松原市</x:v>
       </x:c>
       <x:c r="M58" s="15" t="str">
         <x:v>1</x:v>
@@ -2857,10 +2857,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H59" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I59" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J59" s="2" t="str">
         <x:v>active</x:v>
@@ -2869,7 +2869,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L59" s="14" t="str">
-        <x:v>2000-2024 白城市</x:v>
+        <x:v>1987-1992 白城地区; 1993-2026 白城市</x:v>
       </x:c>
       <x:c r="M59" s="15" t="str">
         <x:v>1</x:v>
@@ -2900,10 +2900,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H60" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I60" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J60" s="2" t="str">
         <x:v>active</x:v>
@@ -2912,7 +2912,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L60" s="14" t="str">
-        <x:v>2000-2024 延边朝鲜族自治州</x:v>
+        <x:v>1987-2026 延边朝鲜族自治州</x:v>
       </x:c>
       <x:c r="M60" s="15" t="str">
         <x:v>0</x:v>
@@ -2943,10 +2943,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H61" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I61" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J61" s="2" t="str">
         <x:v>active</x:v>
@@ -2955,7 +2955,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L61" s="14" t="str">
-        <x:v>2000-2024 哈尔滨市</x:v>
+        <x:v>1987-2026 哈尔滨市</x:v>
       </x:c>
       <x:c r="M61" s="15" t="str">
         <x:v>0</x:v>
@@ -2986,10 +2986,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H62" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I62" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J62" s="2" t="str">
         <x:v>active</x:v>
@@ -2998,7 +2998,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L62" s="14" t="str">
-        <x:v>2000-2024 齐齐哈尔市</x:v>
+        <x:v>1987-2026 齐齐哈尔市</x:v>
       </x:c>
       <x:c r="M62" s="15" t="str">
         <x:v>0</x:v>
@@ -3029,10 +3029,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H63" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I63" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J63" s="2" t="str">
         <x:v>active</x:v>
@@ -3041,7 +3041,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L63" s="14" t="str">
-        <x:v>2000-2024 鸡西市</x:v>
+        <x:v>1987-2026 鸡西市</x:v>
       </x:c>
       <x:c r="M63" s="15" t="str">
         <x:v>0</x:v>
@@ -3072,10 +3072,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H64" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I64" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J64" s="2" t="str">
         <x:v>active</x:v>
@@ -3084,7 +3084,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L64" s="14" t="str">
-        <x:v>2000-2024 鹤岗市</x:v>
+        <x:v>1987-2026 鹤岗市</x:v>
       </x:c>
       <x:c r="M64" s="15" t="str">
         <x:v>0</x:v>
@@ -3115,10 +3115,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H65" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I65" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J65" s="2" t="str">
         <x:v>active</x:v>
@@ -3127,7 +3127,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L65" s="14" t="str">
-        <x:v>2000-2024 双鸭山市</x:v>
+        <x:v>1987-2026 双鸭山市</x:v>
       </x:c>
       <x:c r="M65" s="15" t="str">
         <x:v>0</x:v>
@@ -3158,10 +3158,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H66" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I66" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J66" s="2" t="str">
         <x:v>active</x:v>
@@ -3170,7 +3170,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L66" s="14" t="str">
-        <x:v>2000-2024 大庆市</x:v>
+        <x:v>1987-2026 大庆市</x:v>
       </x:c>
       <x:c r="M66" s="15" t="str">
         <x:v>0</x:v>
@@ -3201,10 +3201,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H67" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I67" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J67" s="2" t="str">
         <x:v>active</x:v>
@@ -3213,7 +3213,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L67" s="14" t="str">
-        <x:v>2000-2024 伊春市</x:v>
+        <x:v>1987-2026 伊春市</x:v>
       </x:c>
       <x:c r="M67" s="15" t="str">
         <x:v>0</x:v>
@@ -3244,10 +3244,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H68" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I68" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J68" s="2" t="str">
         <x:v>active</x:v>
@@ -3256,7 +3256,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L68" s="14" t="str">
-        <x:v>2000-2024 佳木斯市</x:v>
+        <x:v>1987-2026 佳木斯市</x:v>
       </x:c>
       <x:c r="M68" s="15" t="str">
         <x:v>0</x:v>
@@ -3287,10 +3287,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H69" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I69" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J69" s="2" t="str">
         <x:v>active</x:v>
@@ -3299,7 +3299,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L69" s="14" t="str">
-        <x:v>2000-2024 七台河市</x:v>
+        <x:v>1987-2026 七台河市</x:v>
       </x:c>
       <x:c r="M69" s="15" t="str">
         <x:v>0</x:v>
@@ -3330,10 +3330,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H70" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I70" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J70" s="2" t="str">
         <x:v>active</x:v>
@@ -3342,7 +3342,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L70" s="14" t="str">
-        <x:v>2000-2024 牡丹江市</x:v>
+        <x:v>1987-2026 牡丹江市</x:v>
       </x:c>
       <x:c r="M70" s="15" t="str">
         <x:v>0</x:v>
@@ -3373,10 +3373,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H71" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I71" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J71" s="2" t="str">
         <x:v>active</x:v>
@@ -3385,7 +3385,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L71" s="14" t="str">
-        <x:v>2000-2024 黑河市</x:v>
+        <x:v>1987-1992 黑河地区; 1993-2026 黑河市</x:v>
       </x:c>
       <x:c r="M71" s="15" t="str">
         <x:v>1</x:v>
@@ -3416,10 +3416,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H72" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I72" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J72" s="2" t="str">
         <x:v>active</x:v>
@@ -3428,7 +3428,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L72" s="14" t="str">
-        <x:v>2000-2024 绥化市</x:v>
+        <x:v>1987-1998 绥化地区; 1999-2026 绥化市</x:v>
       </x:c>
       <x:c r="M72" s="15" t="str">
         <x:v>1</x:v>
@@ -3459,10 +3459,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H73" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I73" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J73" s="2" t="str">
         <x:v>active</x:v>
@@ -3471,7 +3471,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L73" s="14" t="str">
-        <x:v>2000-2024 大兴安岭地区</x:v>
+        <x:v>1987-2026 大兴安岭地区</x:v>
       </x:c>
       <x:c r="M73" s="15" t="str">
         <x:v>0</x:v>
@@ -3502,10 +3502,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H74" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I74" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J74" s="2" t="str">
         <x:v>active</x:v>
@@ -3514,7 +3514,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L74" s="14" t="str">
-        <x:v>2000-2024 上海市</x:v>
+        <x:v>1987-2026 上海市</x:v>
       </x:c>
       <x:c r="M74" s="15" t="str">
         <x:v>0</x:v>
@@ -3545,10 +3545,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H75" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I75" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J75" s="2" t="str">
         <x:v>active</x:v>
@@ -3557,7 +3557,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L75" s="14" t="str">
-        <x:v>2000-2024 南京市</x:v>
+        <x:v>1987-2026 南京市</x:v>
       </x:c>
       <x:c r="M75" s="15" t="str">
         <x:v>0</x:v>
@@ -3588,10 +3588,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H76" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I76" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J76" s="2" t="str">
         <x:v>active</x:v>
@@ -3600,7 +3600,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L76" s="14" t="str">
-        <x:v>2000-2024 无锡市</x:v>
+        <x:v>1987-2026 无锡市</x:v>
       </x:c>
       <x:c r="M76" s="15" t="str">
         <x:v>0</x:v>
@@ -3631,10 +3631,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H77" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I77" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J77" s="2" t="str">
         <x:v>active</x:v>
@@ -3643,7 +3643,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L77" s="14" t="str">
-        <x:v>2000-2024 徐州市</x:v>
+        <x:v>1987-2026 徐州市</x:v>
       </x:c>
       <x:c r="M77" s="15" t="str">
         <x:v>0</x:v>
@@ -3674,10 +3674,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H78" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I78" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J78" s="2" t="str">
         <x:v>active</x:v>
@@ -3686,7 +3686,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L78" s="14" t="str">
-        <x:v>2000-2024 常州市</x:v>
+        <x:v>1987-2026 常州市</x:v>
       </x:c>
       <x:c r="M78" s="15" t="str">
         <x:v>0</x:v>
@@ -3717,10 +3717,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H79" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I79" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J79" s="2" t="str">
         <x:v>active</x:v>
@@ -3729,7 +3729,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L79" s="14" t="str">
-        <x:v>2000-2024 苏州市</x:v>
+        <x:v>1987-2026 苏州市</x:v>
       </x:c>
       <x:c r="M79" s="15" t="str">
         <x:v>0</x:v>
@@ -3760,10 +3760,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H80" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I80" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J80" s="2" t="str">
         <x:v>active</x:v>
@@ -3772,7 +3772,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L80" s="14" t="str">
-        <x:v>2000-2024 南通市</x:v>
+        <x:v>1987-2026 南通市</x:v>
       </x:c>
       <x:c r="M80" s="15" t="str">
         <x:v>0</x:v>
@@ -3803,10 +3803,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H81" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I81" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J81" s="2" t="str">
         <x:v>active</x:v>
@@ -3815,7 +3815,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L81" s="14" t="str">
-        <x:v>2000-2024 连云港市</x:v>
+        <x:v>1987-2026 连云港市</x:v>
       </x:c>
       <x:c r="M81" s="15" t="str">
         <x:v>0</x:v>
@@ -3846,10 +3846,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H82" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I82" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J82" s="2" t="str">
         <x:v>active</x:v>
@@ -3858,7 +3858,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L82" s="14" t="str">
-        <x:v>2000-2024 淮安市</x:v>
+        <x:v>1987-1999 淮阴市; 2000-2026 淮安市</x:v>
       </x:c>
       <x:c r="M82" s="15" t="str">
         <x:v>1</x:v>
@@ -3889,10 +3889,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H83" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I83" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J83" s="2" t="str">
         <x:v>active</x:v>
@@ -3901,7 +3901,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L83" s="14" t="str">
-        <x:v>2000-2024 盐城市</x:v>
+        <x:v>1987-2026 盐城市</x:v>
       </x:c>
       <x:c r="M83" s="15" t="str">
         <x:v>0</x:v>
@@ -3932,10 +3932,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H84" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I84" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J84" s="2" t="str">
         <x:v>active</x:v>
@@ -3944,7 +3944,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L84" s="14" t="str">
-        <x:v>2000-2024 扬州市</x:v>
+        <x:v>1987-2026 扬州市</x:v>
       </x:c>
       <x:c r="M84" s="15" t="str">
         <x:v>0</x:v>
@@ -3975,10 +3975,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H85" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I85" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J85" s="2" t="str">
         <x:v>active</x:v>
@@ -3987,7 +3987,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L85" s="14" t="str">
-        <x:v>2000-2024 镇江市</x:v>
+        <x:v>1987-2026 镇江市</x:v>
       </x:c>
       <x:c r="M85" s="15" t="str">
         <x:v>0</x:v>
@@ -4018,10 +4018,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H86" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I86" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J86" s="2" t="str">
         <x:v>active</x:v>
@@ -4030,7 +4030,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L86" s="14" t="str">
-        <x:v>2000-2024 泰州市</x:v>
+        <x:v>1987-2026 泰州市</x:v>
       </x:c>
       <x:c r="M86" s="15" t="str">
         <x:v>0</x:v>
@@ -4061,10 +4061,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H87" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I87" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J87" s="2" t="str">
         <x:v>active</x:v>
@@ -4073,7 +4073,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L87" s="14" t="str">
-        <x:v>2000-2024 宿迁市</x:v>
+        <x:v>1987-2026 宿迁市</x:v>
       </x:c>
       <x:c r="M87" s="15" t="str">
         <x:v>0</x:v>
@@ -4104,10 +4104,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H88" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I88" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J88" s="2" t="str">
         <x:v>active</x:v>
@@ -4116,7 +4116,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L88" s="14" t="str">
-        <x:v>2000-2024 杭州市</x:v>
+        <x:v>1987-2026 杭州市</x:v>
       </x:c>
       <x:c r="M88" s="15" t="str">
         <x:v>0</x:v>
@@ -4147,10 +4147,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H89" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I89" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J89" s="2" t="str">
         <x:v>active</x:v>
@@ -4159,7 +4159,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L89" s="14" t="str">
-        <x:v>2000-2024 宁波市</x:v>
+        <x:v>1987-2026 宁波市</x:v>
       </x:c>
       <x:c r="M89" s="15" t="str">
         <x:v>0</x:v>
@@ -4190,10 +4190,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H90" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I90" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J90" s="2" t="str">
         <x:v>active</x:v>
@@ -4202,7 +4202,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L90" s="14" t="str">
-        <x:v>2000-2024 温州市</x:v>
+        <x:v>1987-2026 温州市</x:v>
       </x:c>
       <x:c r="M90" s="15" t="str">
         <x:v>0</x:v>
@@ -4233,10 +4233,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H91" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I91" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J91" s="2" t="str">
         <x:v>active</x:v>
@@ -4245,7 +4245,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L91" s="14" t="str">
-        <x:v>2000-2024 嘉兴市</x:v>
+        <x:v>1987-2026 嘉兴市</x:v>
       </x:c>
       <x:c r="M91" s="15" t="str">
         <x:v>0</x:v>
@@ -4276,10 +4276,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H92" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I92" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J92" s="2" t="str">
         <x:v>active</x:v>
@@ -4288,7 +4288,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L92" s="14" t="str">
-        <x:v>2000-2024 湖州市</x:v>
+        <x:v>1987-2026 湖州市</x:v>
       </x:c>
       <x:c r="M92" s="15" t="str">
         <x:v>0</x:v>
@@ -4319,10 +4319,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H93" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I93" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J93" s="2" t="str">
         <x:v>active</x:v>
@@ -4331,7 +4331,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L93" s="14" t="str">
-        <x:v>2000-2024 绍兴市</x:v>
+        <x:v>1987-2026 绍兴市</x:v>
       </x:c>
       <x:c r="M93" s="15" t="str">
         <x:v>0</x:v>
@@ -4362,10 +4362,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H94" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I94" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J94" s="2" t="str">
         <x:v>active</x:v>
@@ -4374,7 +4374,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L94" s="14" t="str">
-        <x:v>2000-2024 金华市</x:v>
+        <x:v>1987-2026 金华市</x:v>
       </x:c>
       <x:c r="M94" s="15" t="str">
         <x:v>0</x:v>
@@ -4405,10 +4405,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H95" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I95" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J95" s="2" t="str">
         <x:v>active</x:v>
@@ -4417,7 +4417,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L95" s="14" t="str">
-        <x:v>2000-2024 衢州市</x:v>
+        <x:v>1987-2026 衢州市</x:v>
       </x:c>
       <x:c r="M95" s="15" t="str">
         <x:v>0</x:v>
@@ -4448,10 +4448,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H96" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I96" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J96" s="2" t="str">
         <x:v>active</x:v>
@@ -4460,7 +4460,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L96" s="14" t="str">
-        <x:v>2000-2024 舟山市</x:v>
+        <x:v>1987-2026 舟山市</x:v>
       </x:c>
       <x:c r="M96" s="15" t="str">
         <x:v>1</x:v>
@@ -4491,10 +4491,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H97" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I97" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J97" s="2" t="str">
         <x:v>active</x:v>
@@ -4503,7 +4503,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L97" s="14" t="str">
-        <x:v>2000-2024 台州市</x:v>
+        <x:v>1987-1993 台州地区; 1994-2026 台州市</x:v>
       </x:c>
       <x:c r="M97" s="15" t="str">
         <x:v>1</x:v>
@@ -4534,10 +4534,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H98" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I98" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J98" s="2" t="str">
         <x:v>active</x:v>
@@ -4546,7 +4546,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L98" s="14" t="str">
-        <x:v>2000-2024 丽水市</x:v>
+        <x:v>1987-1999 丽水地区; 2000-2026 丽水市</x:v>
       </x:c>
       <x:c r="M98" s="15" t="str">
         <x:v>1</x:v>
@@ -4577,10 +4577,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H99" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I99" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J99" s="2" t="str">
         <x:v>active</x:v>
@@ -4589,7 +4589,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L99" s="14" t="str">
-        <x:v>2000-2024 合肥市</x:v>
+        <x:v>1987-2026 合肥市</x:v>
       </x:c>
       <x:c r="M99" s="15" t="str">
         <x:v>0</x:v>
@@ -4620,10 +4620,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H100" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I100" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J100" s="2" t="str">
         <x:v>active</x:v>
@@ -4632,7 +4632,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L100" s="14" t="str">
-        <x:v>2000-2024 芜湖市</x:v>
+        <x:v>1987-2026 芜湖市</x:v>
       </x:c>
       <x:c r="M100" s="15" t="str">
         <x:v>0</x:v>
@@ -4663,10 +4663,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H101" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I101" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J101" s="2" t="str">
         <x:v>active</x:v>
@@ -4675,7 +4675,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L101" s="14" t="str">
-        <x:v>2000-2024 蚌埠市</x:v>
+        <x:v>1987-2026 蚌埠市</x:v>
       </x:c>
       <x:c r="M101" s="15" t="str">
         <x:v>0</x:v>
@@ -4706,10 +4706,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H102" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I102" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J102" s="2" t="str">
         <x:v>active</x:v>
@@ -4718,7 +4718,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L102" s="14" t="str">
-        <x:v>2000-2024 淮南市</x:v>
+        <x:v>1987-2026 淮南市</x:v>
       </x:c>
       <x:c r="M102" s="15" t="str">
         <x:v>0</x:v>
@@ -4749,10 +4749,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H103" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I103" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J103" s="2" t="str">
         <x:v>active</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L103" s="14" t="str">
-        <x:v>2000-2024 马鞍山市</x:v>
+        <x:v>1987-2026 马鞍山市</x:v>
       </x:c>
       <x:c r="M103" s="15" t="str">
         <x:v>0</x:v>
@@ -4792,10 +4792,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H104" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I104" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J104" s="2" t="str">
         <x:v>active</x:v>
@@ -4804,7 +4804,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L104" s="14" t="str">
-        <x:v>2000-2024 淮北市</x:v>
+        <x:v>1987-2026 淮北市</x:v>
       </x:c>
       <x:c r="M104" s="15" t="str">
         <x:v>0</x:v>
@@ -4835,10 +4835,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H105" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I105" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J105" s="2" t="str">
         <x:v>active</x:v>
@@ -4847,7 +4847,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L105" s="14" t="str">
-        <x:v>2000-2024 铜陵市</x:v>
+        <x:v>1987-2026 铜陵市</x:v>
       </x:c>
       <x:c r="M105" s="15" t="str">
         <x:v>0</x:v>
@@ -4878,10 +4878,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H106" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I106" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J106" s="2" t="str">
         <x:v>active</x:v>
@@ -4890,7 +4890,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L106" s="14" t="str">
-        <x:v>2000-2024 安庆市</x:v>
+        <x:v>1987-2026 安庆市</x:v>
       </x:c>
       <x:c r="M106" s="15" t="str">
         <x:v>1</x:v>
@@ -4921,10 +4921,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H107" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I107" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J107" s="2" t="str">
         <x:v>active</x:v>
@@ -4933,7 +4933,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L107" s="14" t="str">
-        <x:v>2000-2024 黄山市</x:v>
+        <x:v>1987-2026 黄山市</x:v>
       </x:c>
       <x:c r="M107" s="15" t="str">
         <x:v>1</x:v>
@@ -4964,10 +4964,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H108" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I108" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J108" s="2" t="str">
         <x:v>active</x:v>
@@ -4976,7 +4976,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L108" s="14" t="str">
-        <x:v>2000-2024 滁州市</x:v>
+        <x:v>1987-1991 滁县地区; 1992-2026 滁州市</x:v>
       </x:c>
       <x:c r="M108" s="15" t="str">
         <x:v>1</x:v>
@@ -5007,10 +5007,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H109" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I109" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J109" s="2" t="str">
         <x:v>active</x:v>
@@ -5019,7 +5019,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L109" s="14" t="str">
-        <x:v>2000-2024 阜阳市</x:v>
+        <x:v>1987-1995 阜阳地区; 1996-2026 阜阳市</x:v>
       </x:c>
       <x:c r="M109" s="15" t="str">
         <x:v>1</x:v>
@@ -5050,10 +5050,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H110" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I110" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J110" s="2" t="str">
         <x:v>active</x:v>
@@ -5062,7 +5062,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L110" s="14" t="str">
-        <x:v>2000-2024 宿州市</x:v>
+        <x:v>1987-1997 宿县地区; 1998-2026 宿州市</x:v>
       </x:c>
       <x:c r="M110" s="15" t="str">
         <x:v>1</x:v>
@@ -5093,7 +5093,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H111" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I111" s="12" t="str">
         <x:v>2010</x:v>
@@ -5105,7 +5105,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L111" s="14" t="str">
-        <x:v>2000-2010 巢湖市; 2011-2024 [abolished]</x:v>
+        <x:v>1987-1998 巢湖地区; 1999-2010 巢湖市; 2011-2024 [abolished]; 2025-2026 巢湖市</x:v>
       </x:c>
       <x:c r="M111" s="15" t="str">
         <x:v>2</x:v>
@@ -5136,10 +5136,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H112" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I112" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J112" s="2" t="str">
         <x:v>active</x:v>
@@ -5148,7 +5148,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L112" s="14" t="str">
-        <x:v>2000-2024 六安市</x:v>
+        <x:v>1987-1998 六安地区; 1999-2026 六安市</x:v>
       </x:c>
       <x:c r="M112" s="15" t="str">
         <x:v>1</x:v>
@@ -5179,10 +5179,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H113" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I113" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J113" s="2" t="str">
         <x:v>active</x:v>
@@ -5191,7 +5191,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L113" s="14" t="str">
-        <x:v>2000-2024 亳州市</x:v>
+        <x:v>1987-2026 亳州市</x:v>
       </x:c>
       <x:c r="M113" s="15" t="str">
         <x:v>1</x:v>
@@ -5222,10 +5222,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H114" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I114" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J114" s="2" t="str">
         <x:v>active</x:v>
@@ -5234,7 +5234,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L114" s="14" t="str">
-        <x:v>2000-2024 池州市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-1999 池州地区; 2000-2026 池州市</x:v>
       </x:c>
       <x:c r="M114" s="15" t="str">
         <x:v>2</x:v>
@@ -5265,10 +5265,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H115" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I115" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J115" s="2" t="str">
         <x:v>active</x:v>
@@ -5277,7 +5277,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L115" s="14" t="str">
-        <x:v>2000-2024 宣城市</x:v>
+        <x:v>1987-1999 宣城地区; 2000-2026 宣城市</x:v>
       </x:c>
       <x:c r="M115" s="15" t="str">
         <x:v>1</x:v>
@@ -5308,10 +5308,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H116" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I116" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J116" s="2" t="str">
         <x:v>active</x:v>
@@ -5320,7 +5320,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L116" s="14" t="str">
-        <x:v>2000-2024 福州市</x:v>
+        <x:v>1987-2026 福州市</x:v>
       </x:c>
       <x:c r="M116" s="15" t="str">
         <x:v>0</x:v>
@@ -5351,10 +5351,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H117" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I117" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J117" s="2" t="str">
         <x:v>active</x:v>
@@ -5363,7 +5363,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L117" s="14" t="str">
-        <x:v>2000-2024 厦门市</x:v>
+        <x:v>1987-2026 厦门市</x:v>
       </x:c>
       <x:c r="M117" s="15" t="str">
         <x:v>0</x:v>
@@ -5394,10 +5394,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H118" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I118" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J118" s="2" t="str">
         <x:v>active</x:v>
@@ -5406,7 +5406,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L118" s="14" t="str">
-        <x:v>2000-2024 莆田市</x:v>
+        <x:v>1987-2026 莆田市</x:v>
       </x:c>
       <x:c r="M118" s="15" t="str">
         <x:v>0</x:v>
@@ -5437,10 +5437,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H119" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I119" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J119" s="2" t="str">
         <x:v>active</x:v>
@@ -5449,7 +5449,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L119" s="14" t="str">
-        <x:v>2000-2024 三明市</x:v>
+        <x:v>1987-2026 三明市</x:v>
       </x:c>
       <x:c r="M119" s="15" t="str">
         <x:v>0</x:v>
@@ -5480,10 +5480,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H120" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I120" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J120" s="2" t="str">
         <x:v>active</x:v>
@@ -5492,7 +5492,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L120" s="14" t="str">
-        <x:v>2000-2024 泉州市</x:v>
+        <x:v>1987-2026 泉州市</x:v>
       </x:c>
       <x:c r="M120" s="15" t="str">
         <x:v>0</x:v>
@@ -5523,10 +5523,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H121" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I121" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J121" s="2" t="str">
         <x:v>active</x:v>
@@ -5535,7 +5535,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L121" s="14" t="str">
-        <x:v>2000-2024 漳州市</x:v>
+        <x:v>1987-2026 漳州市</x:v>
       </x:c>
       <x:c r="M121" s="15" t="str">
         <x:v>0</x:v>
@@ -5566,10 +5566,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H122" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I122" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J122" s="2" t="str">
         <x:v>active</x:v>
@@ -5578,7 +5578,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L122" s="14" t="str">
-        <x:v>2000-2024 南平市</x:v>
+        <x:v>1987-1987 建阳地区; 1988-1993 南平地区; 1994-2026 南平市</x:v>
       </x:c>
       <x:c r="M122" s="15" t="str">
         <x:v>2</x:v>
@@ -5609,10 +5609,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H123" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I123" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J123" s="2" t="str">
         <x:v>active</x:v>
@@ -5621,7 +5621,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L123" s="14" t="str">
-        <x:v>2000-2024 龙岩市</x:v>
+        <x:v>1987-1995 龙岩地区; 1996-2026 龙岩市</x:v>
       </x:c>
       <x:c r="M123" s="15" t="str">
         <x:v>1</x:v>
@@ -5652,10 +5652,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H124" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I124" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J124" s="2" t="str">
         <x:v>active</x:v>
@@ -5664,7 +5664,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L124" s="14" t="str">
-        <x:v>2000-2024 宁德市</x:v>
+        <x:v>1987-1998 宁德地区; 1999-2026 宁德市</x:v>
       </x:c>
       <x:c r="M124" s="15" t="str">
         <x:v>1</x:v>
@@ -5695,10 +5695,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H125" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I125" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J125" s="2" t="str">
         <x:v>active</x:v>
@@ -5707,7 +5707,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L125" s="14" t="str">
-        <x:v>2000-2024 南昌市</x:v>
+        <x:v>1987-2026 南昌市</x:v>
       </x:c>
       <x:c r="M125" s="15" t="str">
         <x:v>0</x:v>
@@ -5738,10 +5738,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H126" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I126" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J126" s="2" t="str">
         <x:v>active</x:v>
@@ -5750,7 +5750,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L126" s="14" t="str">
-        <x:v>2000-2024 景德镇市</x:v>
+        <x:v>1987-2026 景德镇市</x:v>
       </x:c>
       <x:c r="M126" s="15" t="str">
         <x:v>0</x:v>
@@ -5781,10 +5781,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H127" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I127" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J127" s="2" t="str">
         <x:v>active</x:v>
@@ -5793,7 +5793,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L127" s="14" t="str">
-        <x:v>2000-2024 萍乡市</x:v>
+        <x:v>1987-2026 萍乡市</x:v>
       </x:c>
       <x:c r="M127" s="15" t="str">
         <x:v>0</x:v>
@@ -5824,10 +5824,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H128" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I128" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J128" s="2" t="str">
         <x:v>active</x:v>
@@ -5836,7 +5836,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L128" s="14" t="str">
-        <x:v>2000-2024 九江市</x:v>
+        <x:v>1987-2026 九江市</x:v>
       </x:c>
       <x:c r="M128" s="15" t="str">
         <x:v>0</x:v>
@@ -5867,10 +5867,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H129" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I129" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J129" s="2" t="str">
         <x:v>active</x:v>
@@ -5879,7 +5879,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L129" s="14" t="str">
-        <x:v>2000-2024 新余市</x:v>
+        <x:v>1987-2026 新余市</x:v>
       </x:c>
       <x:c r="M129" s="15" t="str">
         <x:v>0</x:v>
@@ -5910,10 +5910,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H130" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I130" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J130" s="2" t="str">
         <x:v>active</x:v>
@@ -5922,7 +5922,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L130" s="14" t="str">
-        <x:v>2000-2024 鹰潭市</x:v>
+        <x:v>1987-2026 鹰潭市</x:v>
       </x:c>
       <x:c r="M130" s="15" t="str">
         <x:v>0</x:v>
@@ -5953,10 +5953,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H131" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I131" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J131" s="2" t="str">
         <x:v>active</x:v>
@@ -5965,7 +5965,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L131" s="14" t="str">
-        <x:v>2000-2024 赣州市</x:v>
+        <x:v>1987-1997 赣州地区; 1998-2026 赣州市</x:v>
       </x:c>
       <x:c r="M131" s="15" t="str">
         <x:v>1</x:v>
@@ -5996,10 +5996,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H132" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I132" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J132" s="2" t="str">
         <x:v>active</x:v>
@@ -6008,7 +6008,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L132" s="14" t="str">
-        <x:v>2000-2024 吉安市</x:v>
+        <x:v>1987-1999 吉安地区; 2000-2026 吉安市</x:v>
       </x:c>
       <x:c r="M132" s="15" t="str">
         <x:v>1</x:v>
@@ -6039,10 +6039,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H133" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I133" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J133" s="2" t="str">
         <x:v>active</x:v>
@@ -6051,7 +6051,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L133" s="14" t="str">
-        <x:v>2000-2024 宜春市</x:v>
+        <x:v>1987-1999 宜春地区; 2000-2026 宜春市</x:v>
       </x:c>
       <x:c r="M133" s="15" t="str">
         <x:v>1</x:v>
@@ -6082,10 +6082,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H134" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I134" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J134" s="2" t="str">
         <x:v>active</x:v>
@@ -6094,7 +6094,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L134" s="14" t="str">
-        <x:v>2000-2024 抚州市</x:v>
+        <x:v>1987-1999 抚州地区; 2000-2026 抚州市</x:v>
       </x:c>
       <x:c r="M134" s="15" t="str">
         <x:v>1</x:v>
@@ -6125,10 +6125,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H135" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I135" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J135" s="2" t="str">
         <x:v>active</x:v>
@@ -6137,7 +6137,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L135" s="14" t="str">
-        <x:v>2000-2024 上饶市</x:v>
+        <x:v>1987-1999 上饶地区; 2000-2026 上饶市</x:v>
       </x:c>
       <x:c r="M135" s="15" t="str">
         <x:v>1</x:v>
@@ -6168,10 +6168,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H136" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I136" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J136" s="2" t="str">
         <x:v>active</x:v>
@@ -6180,7 +6180,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L136" s="14" t="str">
-        <x:v>2000-2024 济南市</x:v>
+        <x:v>1987-2026 济南市</x:v>
       </x:c>
       <x:c r="M136" s="15" t="str">
         <x:v>0</x:v>
@@ -6211,10 +6211,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H137" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I137" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J137" s="2" t="str">
         <x:v>active</x:v>
@@ -6223,7 +6223,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L137" s="14" t="str">
-        <x:v>2000-2024 青岛市</x:v>
+        <x:v>1987-2026 青岛市</x:v>
       </x:c>
       <x:c r="M137" s="15" t="str">
         <x:v>0</x:v>
@@ -6254,10 +6254,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H138" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I138" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J138" s="2" t="str">
         <x:v>active</x:v>
@@ -6266,7 +6266,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L138" s="14" t="str">
-        <x:v>2000-2024 淄博市</x:v>
+        <x:v>1987-2026 淄博市</x:v>
       </x:c>
       <x:c r="M138" s="15" t="str">
         <x:v>0</x:v>
@@ -6297,10 +6297,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H139" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I139" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J139" s="2" t="str">
         <x:v>active</x:v>
@@ -6309,7 +6309,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L139" s="14" t="str">
-        <x:v>2000-2024 枣庄市</x:v>
+        <x:v>1987-2026 枣庄市</x:v>
       </x:c>
       <x:c r="M139" s="15" t="str">
         <x:v>0</x:v>
@@ -6340,10 +6340,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H140" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I140" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J140" s="2" t="str">
         <x:v>active</x:v>
@@ -6352,7 +6352,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L140" s="14" t="str">
-        <x:v>2000-2024 东营市</x:v>
+        <x:v>1987-2026 东营市</x:v>
       </x:c>
       <x:c r="M140" s="15" t="str">
         <x:v>0</x:v>
@@ -6383,10 +6383,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H141" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I141" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J141" s="2" t="str">
         <x:v>active</x:v>
@@ -6395,7 +6395,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L141" s="14" t="str">
-        <x:v>2000-2024 烟台市</x:v>
+        <x:v>1987-2026 烟台市</x:v>
       </x:c>
       <x:c r="M141" s="15" t="str">
         <x:v>0</x:v>
@@ -6426,10 +6426,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H142" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I142" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J142" s="2" t="str">
         <x:v>active</x:v>
@@ -6438,7 +6438,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L142" s="14" t="str">
-        <x:v>2000-2024 潍坊市</x:v>
+        <x:v>1987-2026 潍坊市</x:v>
       </x:c>
       <x:c r="M142" s="15" t="str">
         <x:v>0</x:v>
@@ -6469,10 +6469,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H143" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I143" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J143" s="2" t="str">
         <x:v>active</x:v>
@@ -6481,7 +6481,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L143" s="14" t="str">
-        <x:v>2000-2024 济宁市</x:v>
+        <x:v>1987-2026 济宁市</x:v>
       </x:c>
       <x:c r="M143" s="15" t="str">
         <x:v>0</x:v>
@@ -6512,10 +6512,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H144" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I144" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J144" s="2" t="str">
         <x:v>active</x:v>
@@ -6524,7 +6524,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L144" s="14" t="str">
-        <x:v>2000-2024 泰安市</x:v>
+        <x:v>1987-2026 泰安市</x:v>
       </x:c>
       <x:c r="M144" s="15" t="str">
         <x:v>0</x:v>
@@ -6555,10 +6555,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H145" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I145" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J145" s="2" t="str">
         <x:v>active</x:v>
@@ -6567,7 +6567,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L145" s="14" t="str">
-        <x:v>2000-2024 威海市</x:v>
+        <x:v>1987-2026 威海市</x:v>
       </x:c>
       <x:c r="M145" s="15" t="str">
         <x:v>0</x:v>
@@ -6598,10 +6598,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H146" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I146" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J146" s="2" t="str">
         <x:v>active</x:v>
@@ -6610,7 +6610,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L146" s="14" t="str">
-        <x:v>2000-2024 日照市</x:v>
+        <x:v>1987-2026 日照市</x:v>
       </x:c>
       <x:c r="M146" s="15" t="str">
         <x:v>0</x:v>
@@ -6641,7 +6641,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H147" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I147" s="12" t="str">
         <x:v>2018</x:v>
@@ -6653,7 +6653,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L147" s="14" t="str">
-        <x:v>2000-2018 莱芜市; 2019-2024 [abolished]</x:v>
+        <x:v>1987-2018 莱芜市; 2019-2026 [abolished]</x:v>
       </x:c>
       <x:c r="M147" s="15" t="str">
         <x:v>1</x:v>
@@ -6684,10 +6684,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H148" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I148" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J148" s="2" t="str">
         <x:v>active</x:v>
@@ -6696,7 +6696,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L148" s="14" t="str">
-        <x:v>2000-2024 临沂市</x:v>
+        <x:v>1987-1993 临沂地区; 1994-2026 临沂市</x:v>
       </x:c>
       <x:c r="M148" s="15" t="str">
         <x:v>1</x:v>
@@ -6727,10 +6727,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H149" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I149" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J149" s="2" t="str">
         <x:v>active</x:v>
@@ -6739,7 +6739,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L149" s="14" t="str">
-        <x:v>2000-2024 德州市</x:v>
+        <x:v>1987-1993 德州地区; 1994-2026 德州市</x:v>
       </x:c>
       <x:c r="M149" s="15" t="str">
         <x:v>1</x:v>
@@ -6770,10 +6770,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H150" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I150" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J150" s="2" t="str">
         <x:v>active</x:v>
@@ -6782,7 +6782,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L150" s="14" t="str">
-        <x:v>2000-2024 聊城市</x:v>
+        <x:v>1987-1996 聊城地区; 1997-2026 聊城市</x:v>
       </x:c>
       <x:c r="M150" s="15" t="str">
         <x:v>1</x:v>
@@ -6813,10 +6813,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H151" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I151" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J151" s="2" t="str">
         <x:v>active</x:v>
@@ -6825,7 +6825,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L151" s="14" t="str">
-        <x:v>2000-2024 滨州市</x:v>
+        <x:v>1987-1991 惠民地区; 1992-1999 滨州地区; 2000-2026 滨州市</x:v>
       </x:c>
       <x:c r="M151" s="15" t="str">
         <x:v>2</x:v>
@@ -6856,10 +6856,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H152" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I152" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J152" s="2" t="str">
         <x:v>active</x:v>
@@ -6868,7 +6868,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L152" s="14" t="str">
-        <x:v>2000-2024 菏泽市</x:v>
+        <x:v>1987-1999 菏泽地区; 2000-2026 菏泽市</x:v>
       </x:c>
       <x:c r="M152" s="15" t="str">
         <x:v>1</x:v>
@@ -6899,10 +6899,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H153" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I153" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J153" s="2" t="str">
         <x:v>active</x:v>
@@ -6911,7 +6911,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L153" s="14" t="str">
-        <x:v>2000-2024 郑州市</x:v>
+        <x:v>1987-2026 郑州市</x:v>
       </x:c>
       <x:c r="M153" s="15" t="str">
         <x:v>0</x:v>
@@ -6942,10 +6942,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H154" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I154" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J154" s="2" t="str">
         <x:v>active</x:v>
@@ -6954,7 +6954,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L154" s="14" t="str">
-        <x:v>2000-2024 开封市</x:v>
+        <x:v>1987-2026 开封市</x:v>
       </x:c>
       <x:c r="M154" s="15" t="str">
         <x:v>0</x:v>
@@ -6985,10 +6985,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H155" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I155" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J155" s="2" t="str">
         <x:v>active</x:v>
@@ -6997,7 +6997,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L155" s="14" t="str">
-        <x:v>2000-2024 洛阳市</x:v>
+        <x:v>1987-2026 洛阳市</x:v>
       </x:c>
       <x:c r="M155" s="15" t="str">
         <x:v>0</x:v>
@@ -7028,10 +7028,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H156" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I156" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J156" s="2" t="str">
         <x:v>active</x:v>
@@ -7040,7 +7040,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L156" s="14" t="str">
-        <x:v>2000-2024 平顶山市</x:v>
+        <x:v>1987-2026 平顶山市</x:v>
       </x:c>
       <x:c r="M156" s="15" t="str">
         <x:v>0</x:v>
@@ -7071,10 +7071,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H157" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I157" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J157" s="2" t="str">
         <x:v>active</x:v>
@@ -7083,7 +7083,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L157" s="14" t="str">
-        <x:v>2000-2024 安阳市</x:v>
+        <x:v>1987-2026 安阳市</x:v>
       </x:c>
       <x:c r="M157" s="15" t="str">
         <x:v>0</x:v>
@@ -7114,10 +7114,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H158" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I158" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J158" s="2" t="str">
         <x:v>active</x:v>
@@ -7126,7 +7126,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L158" s="14" t="str">
-        <x:v>2000-2024 鹤壁市</x:v>
+        <x:v>1987-2026 鹤壁市</x:v>
       </x:c>
       <x:c r="M158" s="15" t="str">
         <x:v>0</x:v>
@@ -7157,10 +7157,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H159" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I159" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J159" s="2" t="str">
         <x:v>active</x:v>
@@ -7169,7 +7169,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L159" s="14" t="str">
-        <x:v>2000-2024 新乡市</x:v>
+        <x:v>1987-2026 新乡市</x:v>
       </x:c>
       <x:c r="M159" s="15" t="str">
         <x:v>0</x:v>
@@ -7200,10 +7200,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H160" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I160" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J160" s="2" t="str">
         <x:v>active</x:v>
@@ -7212,7 +7212,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L160" s="14" t="str">
-        <x:v>2000-2024 焦作市</x:v>
+        <x:v>1987-2026 焦作市</x:v>
       </x:c>
       <x:c r="M160" s="15" t="str">
         <x:v>0</x:v>
@@ -7243,10 +7243,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H161" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I161" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J161" s="2" t="str">
         <x:v>active</x:v>
@@ -7255,7 +7255,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L161" s="14" t="str">
-        <x:v>2000-2024 濮阳市</x:v>
+        <x:v>1987-2026 濮阳市</x:v>
       </x:c>
       <x:c r="M161" s="15" t="str">
         <x:v>0</x:v>
@@ -7286,10 +7286,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H162" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I162" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J162" s="2" t="str">
         <x:v>active</x:v>
@@ -7298,7 +7298,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L162" s="14" t="str">
-        <x:v>2000-2024 许昌市</x:v>
+        <x:v>1987-2026 许昌市</x:v>
       </x:c>
       <x:c r="M162" s="15" t="str">
         <x:v>0</x:v>
@@ -7329,10 +7329,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H163" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I163" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J163" s="2" t="str">
         <x:v>active</x:v>
@@ -7341,7 +7341,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L163" s="14" t="str">
-        <x:v>2000-2024 漯河市</x:v>
+        <x:v>1987-2026 漯河市</x:v>
       </x:c>
       <x:c r="M163" s="15" t="str">
         <x:v>0</x:v>
@@ -7372,10 +7372,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H164" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I164" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J164" s="2" t="str">
         <x:v>active</x:v>
@@ -7384,7 +7384,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L164" s="14" t="str">
-        <x:v>2000-2024 三门峡市</x:v>
+        <x:v>1987-2026 三门峡市</x:v>
       </x:c>
       <x:c r="M164" s="15" t="str">
         <x:v>0</x:v>
@@ -7415,10 +7415,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H165" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I165" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J165" s="2" t="str">
         <x:v>active</x:v>
@@ -7427,7 +7427,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L165" s="14" t="str">
-        <x:v>2000-2024 南阳市</x:v>
+        <x:v>1987-1993 南阳地区; 1994-2026 南阳市</x:v>
       </x:c>
       <x:c r="M165" s="15" t="str">
         <x:v>1</x:v>
@@ -7458,10 +7458,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H166" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I166" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J166" s="2" t="str">
         <x:v>active</x:v>
@@ -7470,7 +7470,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L166" s="14" t="str">
-        <x:v>2000-2024 商丘市</x:v>
+        <x:v>1987-1996 商丘地区; 1997-2026 商丘市</x:v>
       </x:c>
       <x:c r="M166" s="15" t="str">
         <x:v>1</x:v>
@@ -7501,10 +7501,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H167" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I167" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J167" s="2" t="str">
         <x:v>active</x:v>
@@ -7513,7 +7513,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L167" s="14" t="str">
-        <x:v>2000-2024 信阳市</x:v>
+        <x:v>1987-1997 信阳地区; 1998-2026 信阳市</x:v>
       </x:c>
       <x:c r="M167" s="15" t="str">
         <x:v>1</x:v>
@@ -7544,10 +7544,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H168" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I168" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J168" s="2" t="str">
         <x:v>active</x:v>
@@ -7556,7 +7556,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L168" s="14" t="str">
-        <x:v>2000-2024 周口市</x:v>
+        <x:v>1987-1999 周口地区; 2000-2026 周口市</x:v>
       </x:c>
       <x:c r="M168" s="15" t="str">
         <x:v>1</x:v>
@@ -7587,10 +7587,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H169" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I169" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J169" s="2" t="str">
         <x:v>active</x:v>
@@ -7599,7 +7599,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L169" s="14" t="str">
-        <x:v>2000-2024 驻马店市</x:v>
+        <x:v>1987-1999 驻马店地区; 2000-2026 驻马店市</x:v>
       </x:c>
       <x:c r="M169" s="15" t="str">
         <x:v>1</x:v>
@@ -7630,10 +7630,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H170" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I170" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J170" s="2" t="str">
         <x:v>active</x:v>
@@ -7642,7 +7642,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L170" s="14" t="str">
-        <x:v>2000-2024 武汉市</x:v>
+        <x:v>1987-2026 武汉市</x:v>
       </x:c>
       <x:c r="M170" s="15" t="str">
         <x:v>0</x:v>
@@ -7673,10 +7673,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H171" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I171" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J171" s="2" t="str">
         <x:v>active</x:v>
@@ -7685,7 +7685,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L171" s="14" t="str">
-        <x:v>2000-2024 黄石市</x:v>
+        <x:v>1987-2026 黄石市</x:v>
       </x:c>
       <x:c r="M171" s="15" t="str">
         <x:v>0</x:v>
@@ -7716,10 +7716,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H172" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I172" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J172" s="2" t="str">
         <x:v>active</x:v>
@@ -7728,7 +7728,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L172" s="14" t="str">
-        <x:v>2000-2024 十堰市</x:v>
+        <x:v>1987-2026 十堰市</x:v>
       </x:c>
       <x:c r="M172" s="15" t="str">
         <x:v>1</x:v>
@@ -7759,10 +7759,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H173" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I173" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J173" s="2" t="str">
         <x:v>active</x:v>
@@ -7771,7 +7771,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L173" s="14" t="str">
-        <x:v>2000-2024 宜昌市</x:v>
+        <x:v>1987-2026 宜昌市</x:v>
       </x:c>
       <x:c r="M173" s="15" t="str">
         <x:v>1</x:v>
@@ -7802,10 +7802,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H174" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I174" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J174" s="2" t="str">
         <x:v>active</x:v>
@@ -7814,7 +7814,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L174" s="14" t="str">
-        <x:v>2000-2009 襄樊市; 2010-2024 襄阳市</x:v>
+        <x:v>1987-2009 襄樊市; 2010-2026 襄阳市</x:v>
       </x:c>
       <x:c r="M174" s="15" t="str">
         <x:v>1</x:v>
@@ -7845,10 +7845,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H175" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I175" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J175" s="2" t="str">
         <x:v>active</x:v>
@@ -7857,7 +7857,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L175" s="14" t="str">
-        <x:v>2000-2024 鄂州市</x:v>
+        <x:v>1987-2026 鄂州市</x:v>
       </x:c>
       <x:c r="M175" s="15" t="str">
         <x:v>0</x:v>
@@ -7888,10 +7888,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H176" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I176" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J176" s="2" t="str">
         <x:v>active</x:v>
@@ -7900,7 +7900,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L176" s="14" t="str">
-        <x:v>2000-2024 荆门市</x:v>
+        <x:v>1987-2026 荆门市</x:v>
       </x:c>
       <x:c r="M176" s="15" t="str">
         <x:v>0</x:v>
@@ -7931,10 +7931,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H177" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1993</x:v>
       </x:c>
       <x:c r="I177" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J177" s="2" t="str">
         <x:v>active</x:v>
@@ -7943,7 +7943,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L177" s="14" t="str">
-        <x:v>2000-2024 孝感市</x:v>
+        <x:v>1987-1992 [not_established]; 1993-2026 孝感市</x:v>
       </x:c>
       <x:c r="M177" s="15" t="str">
         <x:v>1</x:v>
@@ -7974,10 +7974,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H178" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I178" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J178" s="2" t="str">
         <x:v>active</x:v>
@@ -7986,7 +7986,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L178" s="14" t="str">
-        <x:v>2000-2024 荆州市</x:v>
+        <x:v>1987-1993 荆州地区; 1994-1995 荆沙市; 1996-2026 荆州市</x:v>
       </x:c>
       <x:c r="M178" s="15" t="str">
         <x:v>2</x:v>
@@ -8017,10 +8017,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H179" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I179" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J179" s="2" t="str">
         <x:v>active</x:v>
@@ -8029,7 +8029,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L179" s="14" t="str">
-        <x:v>2000-2024 黄冈市</x:v>
+        <x:v>1987-1994 黄冈地区; 1995-2026 黄冈市</x:v>
       </x:c>
       <x:c r="M179" s="15" t="str">
         <x:v>1</x:v>
@@ -8060,10 +8060,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H180" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I180" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J180" s="2" t="str">
         <x:v>active</x:v>
@@ -8072,7 +8072,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L180" s="14" t="str">
-        <x:v>2000-2024 咸宁市</x:v>
+        <x:v>1987-1997 咸宁地区; 1998-2026 咸宁市</x:v>
       </x:c>
       <x:c r="M180" s="15" t="str">
         <x:v>1</x:v>
@@ -8103,10 +8103,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H181" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I181" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J181" s="2" t="str">
         <x:v>active</x:v>
@@ -8115,7 +8115,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L181" s="14" t="str">
-        <x:v>2000-2024 随州市</x:v>
+        <x:v>1987-2026 随州市</x:v>
       </x:c>
       <x:c r="M181" s="15" t="str">
         <x:v>1</x:v>
@@ -8146,10 +8146,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H182" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I182" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J182" s="2" t="str">
         <x:v>active</x:v>
@@ -8158,7 +8158,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L182" s="14" t="str">
-        <x:v>2000-2024 恩施土家族苗族自治州</x:v>
+        <x:v>1987-1992 鄂西土家族苗族自治州; 1993-2026 恩施土家族苗族自治州</x:v>
       </x:c>
       <x:c r="M182" s="15" t="str">
         <x:v>1</x:v>
@@ -8189,10 +8189,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H183" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I183" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J183" s="2" t="str">
         <x:v>active</x:v>
@@ -8201,7 +8201,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L183" s="14" t="str">
-        <x:v>2000-2024 长沙市</x:v>
+        <x:v>1987-2026 长沙市</x:v>
       </x:c>
       <x:c r="M183" s="15" t="str">
         <x:v>0</x:v>
@@ -8232,10 +8232,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H184" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I184" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J184" s="2" t="str">
         <x:v>active</x:v>
@@ -8244,7 +8244,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L184" s="14" t="str">
-        <x:v>2000-2024 株洲市</x:v>
+        <x:v>1987-2026 株洲市</x:v>
       </x:c>
       <x:c r="M184" s="15" t="str">
         <x:v>0</x:v>
@@ -8275,10 +8275,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H185" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I185" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J185" s="2" t="str">
         <x:v>active</x:v>
@@ -8287,7 +8287,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L185" s="14" t="str">
-        <x:v>2000-2024 湘潭市</x:v>
+        <x:v>1987-2026 湘潭市</x:v>
       </x:c>
       <x:c r="M185" s="15" t="str">
         <x:v>0</x:v>
@@ -8318,10 +8318,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H186" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I186" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J186" s="2" t="str">
         <x:v>active</x:v>
@@ -8330,7 +8330,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L186" s="14" t="str">
-        <x:v>2000-2024 衡阳市</x:v>
+        <x:v>1987-2026 衡阳市</x:v>
       </x:c>
       <x:c r="M186" s="15" t="str">
         <x:v>0</x:v>
@@ -8361,10 +8361,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H187" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I187" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J187" s="2" t="str">
         <x:v>active</x:v>
@@ -8373,7 +8373,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L187" s="14" t="str">
-        <x:v>2000-2024 邵阳市</x:v>
+        <x:v>1987-2026 邵阳市</x:v>
       </x:c>
       <x:c r="M187" s="15" t="str">
         <x:v>0</x:v>
@@ -8404,10 +8404,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H188" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I188" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J188" s="2" t="str">
         <x:v>active</x:v>
@@ -8416,7 +8416,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L188" s="14" t="str">
-        <x:v>2000-2024 岳阳市</x:v>
+        <x:v>1987-2026 岳阳市</x:v>
       </x:c>
       <x:c r="M188" s="15" t="str">
         <x:v>0</x:v>
@@ -8447,10 +8447,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H189" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I189" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J189" s="2" t="str">
         <x:v>active</x:v>
@@ -8459,7 +8459,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L189" s="14" t="str">
-        <x:v>2000-2024 常德市</x:v>
+        <x:v>1987-1987 常德地区; 1988-2026 常德市</x:v>
       </x:c>
       <x:c r="M189" s="15" t="str">
         <x:v>1</x:v>
@@ -8490,10 +8490,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H190" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I190" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J190" s="2" t="str">
         <x:v>active</x:v>
@@ -8502,7 +8502,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L190" s="14" t="str">
-        <x:v>2000-2024 张家界市</x:v>
+        <x:v>1987-1993 大庸市; 1994-2026 张家界市</x:v>
       </x:c>
       <x:c r="M190" s="15" t="str">
         <x:v>1</x:v>
@@ -8533,10 +8533,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H191" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I191" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J191" s="2" t="str">
         <x:v>active</x:v>
@@ -8545,7 +8545,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L191" s="14" t="str">
-        <x:v>2000-2024 益阳市</x:v>
+        <x:v>1987-1993 益阳地区; 1994-2026 益阳市</x:v>
       </x:c>
       <x:c r="M191" s="15" t="str">
         <x:v>1</x:v>
@@ -8576,10 +8576,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H192" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1994</x:v>
       </x:c>
       <x:c r="I192" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J192" s="2" t="str">
         <x:v>active</x:v>
@@ -8588,7 +8588,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L192" s="14" t="str">
-        <x:v>2000-2024 郴州市</x:v>
+        <x:v>1987-1993 [not_established]; 1994-2026 郴州市</x:v>
       </x:c>
       <x:c r="M192" s="15" t="str">
         <x:v>1</x:v>
@@ -8619,10 +8619,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H193" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I193" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J193" s="2" t="str">
         <x:v>active</x:v>
@@ -8631,7 +8631,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L193" s="14" t="str">
-        <x:v>2000-2024 永州市</x:v>
+        <x:v>1987-1994 零陵地区; 1995-2026 永州市</x:v>
       </x:c>
       <x:c r="M193" s="15" t="str">
         <x:v>1</x:v>
@@ -8662,10 +8662,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H194" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I194" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J194" s="2" t="str">
         <x:v>active</x:v>
@@ -8674,7 +8674,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L194" s="14" t="str">
-        <x:v>2000-2024 怀化市</x:v>
+        <x:v>1987-1996 怀化地区; 1997-2026 怀化市</x:v>
       </x:c>
       <x:c r="M194" s="15" t="str">
         <x:v>1</x:v>
@@ -8705,10 +8705,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H195" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I195" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J195" s="2" t="str">
         <x:v>active</x:v>
@@ -8717,7 +8717,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L195" s="14" t="str">
-        <x:v>2000-2024 娄底市</x:v>
+        <x:v>1987-1998 娄底地区; 1999-2026 娄底市</x:v>
       </x:c>
       <x:c r="M195" s="15" t="str">
         <x:v>1</x:v>
@@ -8748,10 +8748,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H196" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I196" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J196" s="2" t="str">
         <x:v>active</x:v>
@@ -8760,7 +8760,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L196" s="14" t="str">
-        <x:v>2000-2024 湘西土家族苗族自治州</x:v>
+        <x:v>1987-2026 湘西土家族苗族自治州</x:v>
       </x:c>
       <x:c r="M196" s="15" t="str">
         <x:v>0</x:v>
@@ -8791,10 +8791,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H197" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I197" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J197" s="2" t="str">
         <x:v>active</x:v>
@@ -8803,7 +8803,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L197" s="14" t="str">
-        <x:v>2000-2024 广州市</x:v>
+        <x:v>1987-2026 广州市</x:v>
       </x:c>
       <x:c r="M197" s="15" t="str">
         <x:v>0</x:v>
@@ -8834,10 +8834,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H198" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I198" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J198" s="2" t="str">
         <x:v>active</x:v>
@@ -8846,7 +8846,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L198" s="14" t="str">
-        <x:v>2000-2024 韶关市</x:v>
+        <x:v>1987-2026 韶关市</x:v>
       </x:c>
       <x:c r="M198" s="15" t="str">
         <x:v>0</x:v>
@@ -8877,10 +8877,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H199" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I199" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J199" s="2" t="str">
         <x:v>active</x:v>
@@ -8889,7 +8889,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L199" s="14" t="str">
-        <x:v>2000-2024 深圳市</x:v>
+        <x:v>1987-2026 深圳市</x:v>
       </x:c>
       <x:c r="M199" s="15" t="str">
         <x:v>0</x:v>
@@ -8920,10 +8920,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H200" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I200" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J200" s="2" t="str">
         <x:v>active</x:v>
@@ -8932,7 +8932,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L200" s="14" t="str">
-        <x:v>2000-2024 珠海市</x:v>
+        <x:v>1987-2026 珠海市</x:v>
       </x:c>
       <x:c r="M200" s="15" t="str">
         <x:v>0</x:v>
@@ -8963,10 +8963,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H201" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I201" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J201" s="2" t="str">
         <x:v>active</x:v>
@@ -8975,7 +8975,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L201" s="14" t="str">
-        <x:v>2000-2024 汕头市</x:v>
+        <x:v>1987-2026 汕头市</x:v>
       </x:c>
       <x:c r="M201" s="15" t="str">
         <x:v>0</x:v>
@@ -9006,10 +9006,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H202" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I202" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J202" s="2" t="str">
         <x:v>active</x:v>
@@ -9018,7 +9018,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L202" s="14" t="str">
-        <x:v>2000-2024 佛山市</x:v>
+        <x:v>1987-2026 佛山市</x:v>
       </x:c>
       <x:c r="M202" s="15" t="str">
         <x:v>0</x:v>
@@ -9049,10 +9049,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H203" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I203" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J203" s="2" t="str">
         <x:v>active</x:v>
@@ -9061,7 +9061,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L203" s="14" t="str">
-        <x:v>2000-2024 江门市</x:v>
+        <x:v>1987-2026 江门市</x:v>
       </x:c>
       <x:c r="M203" s="15" t="str">
         <x:v>0</x:v>
@@ -9092,10 +9092,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H204" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I204" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J204" s="2" t="str">
         <x:v>active</x:v>
@@ -9104,7 +9104,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L204" s="14" t="str">
-        <x:v>2000-2024 湛江市</x:v>
+        <x:v>1987-2026 湛江市</x:v>
       </x:c>
       <x:c r="M204" s="15" t="str">
         <x:v>0</x:v>
@@ -9135,10 +9135,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H205" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I205" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J205" s="2" t="str">
         <x:v>active</x:v>
@@ -9147,7 +9147,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L205" s="14" t="str">
-        <x:v>2000-2024 茂名市</x:v>
+        <x:v>1987-2026 茂名市</x:v>
       </x:c>
       <x:c r="M205" s="15" t="str">
         <x:v>0</x:v>
@@ -9178,10 +9178,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H206" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I206" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J206" s="2" t="str">
         <x:v>active</x:v>
@@ -9190,7 +9190,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L206" s="14" t="str">
-        <x:v>2000-2024 肇庆市</x:v>
+        <x:v>1987-1987 肇庆地区; 1988-2026 肇庆市</x:v>
       </x:c>
       <x:c r="M206" s="15" t="str">
         <x:v>1</x:v>
@@ -9221,10 +9221,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H207" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I207" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J207" s="2" t="str">
         <x:v>active</x:v>
@@ -9233,7 +9233,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L207" s="14" t="str">
-        <x:v>2000-2024 惠州市</x:v>
+        <x:v>1987-1987 惠阳地区; 1988-2026 惠州市</x:v>
       </x:c>
       <x:c r="M207" s="15" t="str">
         <x:v>1</x:v>
@@ -9264,10 +9264,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H208" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I208" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J208" s="2" t="str">
         <x:v>active</x:v>
@@ -9276,7 +9276,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L208" s="14" t="str">
-        <x:v>2000-2024 梅州市</x:v>
+        <x:v>1987-1987 梅县地区; 1988-2026 梅州市</x:v>
       </x:c>
       <x:c r="M208" s="15" t="str">
         <x:v>1</x:v>
@@ -9307,10 +9307,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H209" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I209" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J209" s="2" t="str">
         <x:v>active</x:v>
@@ -9319,7 +9319,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L209" s="14" t="str">
-        <x:v>2000-2024 汕尾市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 汕尾市</x:v>
       </x:c>
       <x:c r="M209" s="15" t="str">
         <x:v>1</x:v>
@@ -9350,10 +9350,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H210" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I210" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J210" s="2" t="str">
         <x:v>active</x:v>
@@ -9362,7 +9362,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L210" s="14" t="str">
-        <x:v>2000-2024 河源市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 河源市</x:v>
       </x:c>
       <x:c r="M210" s="15" t="str">
         <x:v>1</x:v>
@@ -9393,10 +9393,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H211" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I211" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J211" s="2" t="str">
         <x:v>active</x:v>
@@ -9405,7 +9405,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L211" s="14" t="str">
-        <x:v>2000-2024 阳江市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 阳江市</x:v>
       </x:c>
       <x:c r="M211" s="15" t="str">
         <x:v>1</x:v>
@@ -9436,10 +9436,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H212" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I212" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J212" s="2" t="str">
         <x:v>active</x:v>
@@ -9448,7 +9448,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L212" s="14" t="str">
-        <x:v>2000-2024 清远市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 清远市</x:v>
       </x:c>
       <x:c r="M212" s="15" t="str">
         <x:v>1</x:v>
@@ -9479,10 +9479,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H213" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I213" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J213" s="2" t="str">
         <x:v>active</x:v>
@@ -9491,7 +9491,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L213" s="14" t="str">
-        <x:v>2000-2024 东莞市</x:v>
+        <x:v>1987-2026 东莞市</x:v>
       </x:c>
       <x:c r="M213" s="15" t="str">
         <x:v>0</x:v>
@@ -9522,10 +9522,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H214" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I214" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J214" s="2" t="str">
         <x:v>active</x:v>
@@ -9534,7 +9534,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L214" s="14" t="str">
-        <x:v>2000-2024 中山市</x:v>
+        <x:v>1987-2026 中山市</x:v>
       </x:c>
       <x:c r="M214" s="15" t="str">
         <x:v>0</x:v>
@@ -9565,10 +9565,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H215" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I215" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J215" s="2" t="str">
         <x:v>active</x:v>
@@ -9577,7 +9577,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L215" s="14" t="str">
-        <x:v>2000-2024 潮州市</x:v>
+        <x:v>1987-2026 潮州市</x:v>
       </x:c>
       <x:c r="M215" s="15" t="str">
         <x:v>0</x:v>
@@ -9608,10 +9608,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H216" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I216" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J216" s="2" t="str">
         <x:v>active</x:v>
@@ -9620,7 +9620,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L216" s="14" t="str">
-        <x:v>2000-2024 揭阳市</x:v>
+        <x:v>1987-2026 揭阳市</x:v>
       </x:c>
       <x:c r="M216" s="15" t="str">
         <x:v>0</x:v>
@@ -9651,10 +9651,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H217" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I217" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J217" s="2" t="str">
         <x:v>active</x:v>
@@ -9663,7 +9663,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L217" s="14" t="str">
-        <x:v>2000-2024 云浮市</x:v>
+        <x:v>1987-2026 云浮市</x:v>
       </x:c>
       <x:c r="M217" s="15" t="str">
         <x:v>0</x:v>
@@ -9694,10 +9694,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H218" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I218" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J218" s="2" t="str">
         <x:v>active</x:v>
@@ -9706,7 +9706,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L218" s="14" t="str">
-        <x:v>2000-2024 南宁市</x:v>
+        <x:v>1987-2026 南宁市</x:v>
       </x:c>
       <x:c r="M218" s="15" t="str">
         <x:v>0</x:v>
@@ -9737,10 +9737,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H219" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I219" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J219" s="2" t="str">
         <x:v>active</x:v>
@@ -9749,7 +9749,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L219" s="14" t="str">
-        <x:v>2000-2024 柳州市</x:v>
+        <x:v>1987-2026 柳州市</x:v>
       </x:c>
       <x:c r="M219" s="15" t="str">
         <x:v>0</x:v>
@@ -9780,10 +9780,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H220" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I220" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J220" s="2" t="str">
         <x:v>active</x:v>
@@ -9792,7 +9792,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L220" s="14" t="str">
-        <x:v>2000-2024 桂林市</x:v>
+        <x:v>1987-2026 桂林市</x:v>
       </x:c>
       <x:c r="M220" s="15" t="str">
         <x:v>0</x:v>
@@ -9823,10 +9823,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H221" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I221" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J221" s="2" t="str">
         <x:v>active</x:v>
@@ -9835,7 +9835,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L221" s="14" t="str">
-        <x:v>2000-2024 梧州市</x:v>
+        <x:v>1987-2026 梧州市</x:v>
       </x:c>
       <x:c r="M221" s="15" t="str">
         <x:v>0</x:v>
@@ -9866,10 +9866,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H222" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I222" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J222" s="2" t="str">
         <x:v>active</x:v>
@@ -9878,7 +9878,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L222" s="14" t="str">
-        <x:v>2000-2024 北海市</x:v>
+        <x:v>1987-2026 北海市</x:v>
       </x:c>
       <x:c r="M222" s="15" t="str">
         <x:v>0</x:v>
@@ -9909,10 +9909,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H223" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1993</x:v>
       </x:c>
       <x:c r="I223" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J223" s="2" t="str">
         <x:v>active</x:v>
@@ -9921,7 +9921,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L223" s="14" t="str">
-        <x:v>2000-2024 防城港市</x:v>
+        <x:v>1987-1992 [not_established]; 1993-2026 防城港市</x:v>
       </x:c>
       <x:c r="M223" s="15" t="str">
         <x:v>1</x:v>
@@ -9952,10 +9952,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H224" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I224" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J224" s="2" t="str">
         <x:v>active</x:v>
@@ -9964,7 +9964,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L224" s="14" t="str">
-        <x:v>2000-2024 钦州市</x:v>
+        <x:v>1987-1993 钦州地区; 1994-2026 钦州市</x:v>
       </x:c>
       <x:c r="M224" s="15" t="str">
         <x:v>1</x:v>
@@ -9995,10 +9995,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H225" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I225" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J225" s="2" t="str">
         <x:v>active</x:v>
@@ -10007,7 +10007,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L225" s="14" t="str">
-        <x:v>2000-2024 贵港市</x:v>
+        <x:v>1987-2026 贵港市</x:v>
       </x:c>
       <x:c r="M225" s="15" t="str">
         <x:v>0</x:v>
@@ -10038,10 +10038,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H226" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I226" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J226" s="2" t="str">
         <x:v>active</x:v>
@@ -10050,7 +10050,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L226" s="14" t="str">
-        <x:v>2000-2024 玉林市</x:v>
+        <x:v>1987-1996 玉林地区; 1997-2026 玉林市</x:v>
       </x:c>
       <x:c r="M226" s="15" t="str">
         <x:v>1</x:v>
@@ -10081,10 +10081,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H227" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I227" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J227" s="2" t="str">
         <x:v>active</x:v>
@@ -10093,7 +10093,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L227" s="14" t="str">
-        <x:v>2000-2001 百色地区; 2002-2024 百色市</x:v>
+        <x:v>1987-2001 百色地区; 2002-2026 百色市</x:v>
       </x:c>
       <x:c r="M227" s="15" t="str">
         <x:v>1</x:v>
@@ -10124,10 +10124,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H228" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I228" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J228" s="2" t="str">
         <x:v>active</x:v>
@@ -10136,7 +10136,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L228" s="14" t="str">
-        <x:v>2000-2001 贺州地区; 2002-2024 贺州市</x:v>
+        <x:v>1987-1996 梧州地区; 1997-2001 贺州地区; 2002-2026 贺州市</x:v>
       </x:c>
       <x:c r="M228" s="15" t="str">
         <x:v>2</x:v>
@@ -10167,10 +10167,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H229" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I229" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J229" s="2" t="str">
         <x:v>active</x:v>
@@ -10179,7 +10179,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L229" s="14" t="str">
-        <x:v>2000-2001 河池地区; 2002-2024 河池市</x:v>
+        <x:v>1987-2001 河池地区; 2002-2026 河池市</x:v>
       </x:c>
       <x:c r="M229" s="15" t="str">
         <x:v>1</x:v>
@@ -10210,10 +10210,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H230" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I230" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J230" s="2" t="str">
         <x:v>active</x:v>
@@ -10222,7 +10222,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L230" s="14" t="str">
-        <x:v>2000-2001 柳州地区; 2002-2024 来宾市</x:v>
+        <x:v>1987-2001 柳州地区; 2002-2026 来宾市</x:v>
       </x:c>
       <x:c r="M230" s="15" t="str">
         <x:v>1</x:v>
@@ -10253,10 +10253,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H231" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I231" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J231" s="2" t="str">
         <x:v>active</x:v>
@@ -10265,7 +10265,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L231" s="14" t="str">
-        <x:v>2000-2001 南宁地区; 2002-2024 崇左市</x:v>
+        <x:v>1987-2001 南宁地区; 2002-2026 崇左市</x:v>
       </x:c>
       <x:c r="M231" s="15" t="str">
         <x:v>1</x:v>
@@ -10296,10 +10296,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H232" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I232" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J232" s="2" t="str">
         <x:v>active</x:v>
@@ -10308,7 +10308,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L232" s="14" t="str">
-        <x:v>2000-2024 海口市</x:v>
+        <x:v>1987-2026 海口市</x:v>
       </x:c>
       <x:c r="M232" s="15" t="str">
         <x:v>0</x:v>
@@ -10339,10 +10339,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H233" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I233" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J233" s="2" t="str">
         <x:v>active</x:v>
@@ -10351,7 +10351,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L233" s="14" t="str">
-        <x:v>2000-2024 三亚市</x:v>
+        <x:v>1987-2026 三亚市</x:v>
       </x:c>
       <x:c r="M233" s="15" t="str">
         <x:v>0</x:v>
@@ -10385,7 +10385,7 @@
         <x:v>2012</x:v>
       </x:c>
       <x:c r="I234" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J234" s="2" t="str">
         <x:v>active</x:v>
@@ -10394,7 +10394,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L234" s="14" t="str">
-        <x:v>2000-2011 [not_established]; 2012-2024 三沙市</x:v>
+        <x:v>1987-1999 [not_established]; 2000-2011 [not_established]; 2012-2026 三沙市</x:v>
       </x:c>
       <x:c r="M234" s="15" t="str">
         <x:v>1</x:v>
@@ -10425,10 +10425,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H235" s="12" t="str">
-        <x:v>2015</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I235" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J235" s="2" t="str">
         <x:v>active</x:v>
@@ -10437,7 +10437,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L235" s="14" t="str">
-        <x:v>2000-2014 [not_prefecture_level]; 2015-2024 儋州市</x:v>
+        <x:v>1987-1999 儋州市; 2000-2014 [not_prefecture_level]; 2015-2026 儋州市</x:v>
       </x:c>
       <x:c r="M235" s="15" t="str">
         <x:v>1</x:v>
@@ -10468,10 +10468,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H236" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I236" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J236" s="2" t="str">
         <x:v>active</x:v>
@@ -10480,7 +10480,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L236" s="14" t="str">
-        <x:v>2000-2024 重庆市</x:v>
+        <x:v>1987-2026 重庆市</x:v>
       </x:c>
       <x:c r="M236" s="15" t="str">
         <x:v>0</x:v>
@@ -10511,10 +10511,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H237" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I237" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J237" s="2" t="str">
         <x:v>active</x:v>
@@ -10523,7 +10523,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L237" s="14" t="str">
-        <x:v>2000-2024 成都市</x:v>
+        <x:v>1987-2026 成都市</x:v>
       </x:c>
       <x:c r="M237" s="15" t="str">
         <x:v>0</x:v>
@@ -10554,10 +10554,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H238" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I238" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J238" s="2" t="str">
         <x:v>active</x:v>
@@ -10566,7 +10566,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L238" s="14" t="str">
-        <x:v>2000-2024 自贡市</x:v>
+        <x:v>1987-2026 自贡市</x:v>
       </x:c>
       <x:c r="M238" s="15" t="str">
         <x:v>0</x:v>
@@ -10597,10 +10597,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H239" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I239" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J239" s="2" t="str">
         <x:v>active</x:v>
@@ -10609,7 +10609,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L239" s="14" t="str">
-        <x:v>2000-2024 攀枝花市</x:v>
+        <x:v>1987-2026 攀枝花市</x:v>
       </x:c>
       <x:c r="M239" s="15" t="str">
         <x:v>1</x:v>
@@ -10640,10 +10640,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H240" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I240" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J240" s="2" t="str">
         <x:v>active</x:v>
@@ -10652,7 +10652,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L240" s="14" t="str">
-        <x:v>2000-2024 泸州市</x:v>
+        <x:v>1987-2026 泸州市</x:v>
       </x:c>
       <x:c r="M240" s="15" t="str">
         <x:v>0</x:v>
@@ -10683,10 +10683,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H241" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I241" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J241" s="2" t="str">
         <x:v>active</x:v>
@@ -10695,7 +10695,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L241" s="14" t="str">
-        <x:v>2000-2024 德阳市</x:v>
+        <x:v>1987-2026 德阳市</x:v>
       </x:c>
       <x:c r="M241" s="15" t="str">
         <x:v>0</x:v>
@@ -10726,10 +10726,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H242" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I242" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J242" s="2" t="str">
         <x:v>active</x:v>
@@ -10738,7 +10738,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L242" s="14" t="str">
-        <x:v>2000-2024 绵阳市</x:v>
+        <x:v>1987-2026 绵阳市</x:v>
       </x:c>
       <x:c r="M242" s="15" t="str">
         <x:v>0</x:v>
@@ -10769,10 +10769,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H243" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I243" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J243" s="2" t="str">
         <x:v>active</x:v>
@@ -10781,7 +10781,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L243" s="14" t="str">
-        <x:v>2000-2024 广元市</x:v>
+        <x:v>1987-2026 广元市</x:v>
       </x:c>
       <x:c r="M243" s="15" t="str">
         <x:v>0</x:v>
@@ -10812,10 +10812,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H244" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I244" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J244" s="2" t="str">
         <x:v>active</x:v>
@@ -10824,7 +10824,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L244" s="14" t="str">
-        <x:v>2000-2024 遂宁市</x:v>
+        <x:v>1987-2026 遂宁市</x:v>
       </x:c>
       <x:c r="M244" s="15" t="str">
         <x:v>0</x:v>
@@ -10855,10 +10855,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H245" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I245" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J245" s="2" t="str">
         <x:v>active</x:v>
@@ -10867,7 +10867,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L245" s="14" t="str">
-        <x:v>2000-2024 内江市</x:v>
+        <x:v>1987-2026 内江市</x:v>
       </x:c>
       <x:c r="M245" s="15" t="str">
         <x:v>0</x:v>
@@ -10898,10 +10898,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H246" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I246" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J246" s="2" t="str">
         <x:v>active</x:v>
@@ -10910,7 +10910,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L246" s="14" t="str">
-        <x:v>2000-2024 乐山市</x:v>
+        <x:v>1987-2026 乐山市</x:v>
       </x:c>
       <x:c r="M246" s="15" t="str">
         <x:v>0</x:v>
@@ -10941,10 +10941,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H247" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I247" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J247" s="2" t="str">
         <x:v>active</x:v>
@@ -10953,7 +10953,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L247" s="14" t="str">
-        <x:v>2000-2024 南充市</x:v>
+        <x:v>1987-1992 南充地区; 1993-2026 南充市</x:v>
       </x:c>
       <x:c r="M247" s="15" t="str">
         <x:v>1</x:v>
@@ -10984,10 +10984,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H248" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1997</x:v>
       </x:c>
       <x:c r="I248" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J248" s="2" t="str">
         <x:v>active</x:v>
@@ -10996,7 +10996,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L248" s="14" t="str">
-        <x:v>2000-2024 眉山市</x:v>
+        <x:v>1987-1996 [not_established]; 1997-1999 眉山地区; 2000-2026 眉山市</x:v>
       </x:c>
       <x:c r="M248" s="15" t="str">
         <x:v>2</x:v>
@@ -11027,10 +11027,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H249" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I249" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J249" s="2" t="str">
         <x:v>active</x:v>
@@ -11039,7 +11039,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L249" s="14" t="str">
-        <x:v>2000-2024 宜宾市</x:v>
+        <x:v>1987-1995 宜宾地区; 1996-2026 宜宾市</x:v>
       </x:c>
       <x:c r="M249" s="15" t="str">
         <x:v>1</x:v>
@@ -11070,10 +11070,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H250" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I250" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J250" s="2" t="str">
         <x:v>active</x:v>
@@ -11082,7 +11082,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L250" s="14" t="str">
-        <x:v>2000-2024 广安市</x:v>
+        <x:v>1987-1997 广安地区; 1998-2026 广安市</x:v>
       </x:c>
       <x:c r="M250" s="15" t="str">
         <x:v>1</x:v>
@@ -11113,10 +11113,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H251" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I251" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J251" s="2" t="str">
         <x:v>active</x:v>
@@ -11125,7 +11125,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L251" s="14" t="str">
-        <x:v>2000-2024 达州市</x:v>
+        <x:v>1987-1998 达川地区; 1999-2026 达州市</x:v>
       </x:c>
       <x:c r="M251" s="15" t="str">
         <x:v>1</x:v>
@@ -11156,10 +11156,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H252" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I252" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J252" s="2" t="str">
         <x:v>active</x:v>
@@ -11168,7 +11168,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L252" s="14" t="str">
-        <x:v>2000-2024 雅安市</x:v>
+        <x:v>1987-1999 雅安地区; 2000-2026 雅安市</x:v>
       </x:c>
       <x:c r="M252" s="15" t="str">
         <x:v>1</x:v>
@@ -11199,10 +11199,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H253" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I253" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J253" s="2" t="str">
         <x:v>active</x:v>
@@ -11211,7 +11211,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L253" s="14" t="str">
-        <x:v>2000-2024 巴中市</x:v>
+        <x:v>1987-1999 巴中地区; 2000-2026 巴中市</x:v>
       </x:c>
       <x:c r="M253" s="15" t="str">
         <x:v>1</x:v>
@@ -11242,10 +11242,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H254" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1998</x:v>
       </x:c>
       <x:c r="I254" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J254" s="2" t="str">
         <x:v>active</x:v>
@@ -11254,7 +11254,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L254" s="14" t="str">
-        <x:v>2000-2024 资阳市</x:v>
+        <x:v>1987-1997 [not_established]; 1998-1999 资阳地区; 2000-2026 资阳市</x:v>
       </x:c>
       <x:c r="M254" s="15" t="str">
         <x:v>2</x:v>
@@ -11285,10 +11285,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H255" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I255" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J255" s="2" t="str">
         <x:v>active</x:v>
@@ -11297,7 +11297,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L255" s="14" t="str">
-        <x:v>2000-2024 阿坝藏族羌族自治州</x:v>
+        <x:v>1987-2026 阿坝藏族羌族自治州</x:v>
       </x:c>
       <x:c r="M255" s="15" t="str">
         <x:v>1</x:v>
@@ -11328,10 +11328,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H256" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I256" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J256" s="2" t="str">
         <x:v>active</x:v>
@@ -11340,7 +11340,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L256" s="14" t="str">
-        <x:v>2000-2024 甘孜藏族自治州</x:v>
+        <x:v>1987-2026 甘孜藏族自治州</x:v>
       </x:c>
       <x:c r="M256" s="15" t="str">
         <x:v>0</x:v>
@@ -11371,10 +11371,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H257" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I257" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J257" s="2" t="str">
         <x:v>active</x:v>
@@ -11383,7 +11383,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L257" s="14" t="str">
-        <x:v>2000-2024 凉山彝族自治州</x:v>
+        <x:v>1987-2026 凉山彝族自治州</x:v>
       </x:c>
       <x:c r="M257" s="15" t="str">
         <x:v>0</x:v>
@@ -11414,10 +11414,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H258" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I258" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J258" s="2" t="str">
         <x:v>active</x:v>
@@ -11426,7 +11426,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L258" s="14" t="str">
-        <x:v>2000-2024 贵阳市</x:v>
+        <x:v>1987-2026 贵阳市</x:v>
       </x:c>
       <x:c r="M258" s="15" t="str">
         <x:v>0</x:v>
@@ -11457,10 +11457,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H259" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I259" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J259" s="2" t="str">
         <x:v>active</x:v>
@@ -11469,7 +11469,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L259" s="14" t="str">
-        <x:v>2000-2024 六盘水市</x:v>
+        <x:v>1987-2026 六盘水市</x:v>
       </x:c>
       <x:c r="M259" s="15" t="str">
         <x:v>0</x:v>
@@ -11500,10 +11500,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H260" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I260" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J260" s="2" t="str">
         <x:v>active</x:v>
@@ -11512,7 +11512,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L260" s="14" t="str">
-        <x:v>2000-2024 遵义市</x:v>
+        <x:v>1987-1996 遵义地区; 1997-2026 遵义市</x:v>
       </x:c>
       <x:c r="M260" s="15" t="str">
         <x:v>1</x:v>
@@ -11543,10 +11543,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H261" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I261" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J261" s="2" t="str">
         <x:v>active</x:v>
@@ -11555,7 +11555,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L261" s="14" t="str">
-        <x:v>2000-2024 安顺市</x:v>
+        <x:v>1987-1999 安顺地区; 2000-2026 安顺市</x:v>
       </x:c>
       <x:c r="M261" s="15" t="str">
         <x:v>1</x:v>
@@ -11586,10 +11586,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H262" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I262" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J262" s="2" t="str">
         <x:v>active</x:v>
@@ -11598,7 +11598,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L262" s="14" t="str">
-        <x:v>2000-2010 毕节地区; 2011-2024 毕节市</x:v>
+        <x:v>1987-2010 毕节地区; 2011-2026 毕节市</x:v>
       </x:c>
       <x:c r="M262" s="15" t="str">
         <x:v>1</x:v>
@@ -11629,10 +11629,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H263" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I263" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J263" s="2" t="str">
         <x:v>active</x:v>
@@ -11641,7 +11641,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L263" s="14" t="str">
-        <x:v>2000-2010 铜仁地区; 2011-2024 铜仁市</x:v>
+        <x:v>1987-2010 铜仁地区; 2011-2026 铜仁市</x:v>
       </x:c>
       <x:c r="M263" s="15" t="str">
         <x:v>1</x:v>
@@ -11672,10 +11672,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H264" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I264" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J264" s="2" t="str">
         <x:v>active</x:v>
@@ -11684,7 +11684,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L264" s="14" t="str">
-        <x:v>2000-2024 黔西南布依族苗族自治州</x:v>
+        <x:v>1987-2026 黔西南布依族苗族自治州</x:v>
       </x:c>
       <x:c r="M264" s="15" t="str">
         <x:v>0</x:v>
@@ -11715,10 +11715,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H265" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I265" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J265" s="2" t="str">
         <x:v>active</x:v>
@@ -11727,7 +11727,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L265" s="14" t="str">
-        <x:v>2000-2024 黔东南苗族侗族自治州</x:v>
+        <x:v>1987-2026 黔东南苗族侗族自治州</x:v>
       </x:c>
       <x:c r="M265" s="15" t="str">
         <x:v>0</x:v>
@@ -11758,10 +11758,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H266" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I266" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J266" s="2" t="str">
         <x:v>active</x:v>
@@ -11770,7 +11770,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L266" s="14" t="str">
-        <x:v>2000-2024 黔南布依族苗族自治州</x:v>
+        <x:v>1987-2026 黔南布依族苗族自治州</x:v>
       </x:c>
       <x:c r="M266" s="15" t="str">
         <x:v>0</x:v>
@@ -11801,10 +11801,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H267" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I267" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J267" s="2" t="str">
         <x:v>active</x:v>
@@ -11813,7 +11813,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L267" s="14" t="str">
-        <x:v>2000-2024 昆明市</x:v>
+        <x:v>1987-2026 昆明市</x:v>
       </x:c>
       <x:c r="M267" s="15" t="str">
         <x:v>0</x:v>
@@ -11844,10 +11844,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H268" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I268" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J268" s="2" t="str">
         <x:v>active</x:v>
@@ -11856,7 +11856,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L268" s="14" t="str">
-        <x:v>2000-2024 曲靖市</x:v>
+        <x:v>1987-1996 曲靖地区; 1997-2026 曲靖市</x:v>
       </x:c>
       <x:c r="M268" s="15" t="str">
         <x:v>1</x:v>
@@ -11887,10 +11887,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H269" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I269" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J269" s="2" t="str">
         <x:v>active</x:v>
@@ -11899,7 +11899,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L269" s="14" t="str">
-        <x:v>2000-2024 玉溪市</x:v>
+        <x:v>1987-1996 玉溪地区; 1997-2026 玉溪市</x:v>
       </x:c>
       <x:c r="M269" s="15" t="str">
         <x:v>1</x:v>
@@ -11930,10 +11930,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H270" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I270" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J270" s="2" t="str">
         <x:v>active</x:v>
@@ -11942,7 +11942,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L270" s="14" t="str">
-        <x:v>2000-2024 保山市</x:v>
+        <x:v>1987-1999 保山地区; 2000-2026 保山市</x:v>
       </x:c>
       <x:c r="M270" s="15" t="str">
         <x:v>1</x:v>
@@ -11973,10 +11973,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H271" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I271" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J271" s="2" t="str">
         <x:v>active</x:v>
@@ -11985,7 +11985,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L271" s="14" t="str">
-        <x:v>2000-2000 昭通地区; 2001-2024 昭通市</x:v>
+        <x:v>1987-2000 昭通地区; 2001-2026 昭通市</x:v>
       </x:c>
       <x:c r="M271" s="15" t="str">
         <x:v>1</x:v>
@@ -12016,10 +12016,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H272" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I272" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J272" s="2" t="str">
         <x:v>active</x:v>
@@ -12028,7 +12028,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L272" s="14" t="str">
-        <x:v>2000-2001 丽江地区; 2002-2024 丽江市</x:v>
+        <x:v>1987-2001 丽江地区; 2002-2026 丽江市</x:v>
       </x:c>
       <x:c r="M272" s="15" t="str">
         <x:v>1</x:v>
@@ -12059,10 +12059,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H273" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I273" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J273" s="2" t="str">
         <x:v>active</x:v>
@@ -12071,7 +12071,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L273" s="14" t="str">
-        <x:v>2000-2002 思茅地区; 2003-2006 思茅市; 2007-2024 普洱市</x:v>
+        <x:v>1987-2002 思茅地区; 2003-2006 思茅市; 2007-2026 普洱市</x:v>
       </x:c>
       <x:c r="M273" s="15" t="str">
         <x:v>2</x:v>
@@ -12102,10 +12102,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H274" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I274" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J274" s="2" t="str">
         <x:v>active</x:v>
@@ -12114,7 +12114,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L274" s="14" t="str">
-        <x:v>2000-2002 临沧地区; 2003-2024 临沧市</x:v>
+        <x:v>1987-1999 临沧市; 2000-2002 临沧地区; 2003-2026 临沧市</x:v>
       </x:c>
       <x:c r="M274" s="15" t="str">
         <x:v>0</x:v>
@@ -12145,10 +12145,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H275" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I275" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J275" s="2" t="str">
         <x:v>active</x:v>
@@ -12157,7 +12157,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L275" s="14" t="str">
-        <x:v>2000-2024 楚雄彝族自治州</x:v>
+        <x:v>1987-2026 楚雄彝族自治州</x:v>
       </x:c>
       <x:c r="M275" s="15" t="str">
         <x:v>0</x:v>
@@ -12188,10 +12188,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H276" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I276" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J276" s="2" t="str">
         <x:v>active</x:v>
@@ -12200,7 +12200,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L276" s="14" t="str">
-        <x:v>2000-2024 红河哈尼族彝族自治州</x:v>
+        <x:v>1987-2026 红河哈尼族彝族自治州</x:v>
       </x:c>
       <x:c r="M276" s="15" t="str">
         <x:v>0</x:v>
@@ -12231,10 +12231,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H277" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I277" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J277" s="2" t="str">
         <x:v>active</x:v>
@@ -12243,7 +12243,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L277" s="14" t="str">
-        <x:v>2000-2024 文山壮族苗族自治州</x:v>
+        <x:v>1987-2026 文山壮族苗族自治州</x:v>
       </x:c>
       <x:c r="M277" s="15" t="str">
         <x:v>0</x:v>
@@ -12274,10 +12274,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H278" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I278" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J278" s="2" t="str">
         <x:v>active</x:v>
@@ -12286,7 +12286,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L278" s="14" t="str">
-        <x:v>2000-2024 西双版纳傣族自治州</x:v>
+        <x:v>1987-2026 西双版纳傣族自治州</x:v>
       </x:c>
       <x:c r="M278" s="15" t="str">
         <x:v>0</x:v>
@@ -12317,10 +12317,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H279" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I279" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J279" s="2" t="str">
         <x:v>active</x:v>
@@ -12329,7 +12329,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L279" s="14" t="str">
-        <x:v>2000-2024 大理白族自治州</x:v>
+        <x:v>1987-2026 大理白族自治州</x:v>
       </x:c>
       <x:c r="M279" s="15" t="str">
         <x:v>0</x:v>
@@ -12360,10 +12360,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H280" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I280" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J280" s="2" t="str">
         <x:v>active</x:v>
@@ -12372,7 +12372,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L280" s="14" t="str">
-        <x:v>2000-2024 德宏傣族景颇族自治州</x:v>
+        <x:v>1987-2026 德宏傣族景颇族自治州</x:v>
       </x:c>
       <x:c r="M280" s="15" t="str">
         <x:v>0</x:v>
@@ -12403,10 +12403,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H281" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I281" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J281" s="2" t="str">
         <x:v>active</x:v>
@@ -12415,7 +12415,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L281" s="14" t="str">
-        <x:v>2000-2024 怒江傈僳族自治州</x:v>
+        <x:v>1987-2026 怒江傈僳族自治州</x:v>
       </x:c>
       <x:c r="M281" s="15" t="str">
         <x:v>0</x:v>
@@ -12446,10 +12446,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H282" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I282" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J282" s="2" t="str">
         <x:v>active</x:v>
@@ -12458,7 +12458,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L282" s="14" t="str">
-        <x:v>2000-2024 迪庆藏族自治州</x:v>
+        <x:v>1987-2026 迪庆藏族自治州</x:v>
       </x:c>
       <x:c r="M282" s="15" t="str">
         <x:v>0</x:v>
@@ -12489,10 +12489,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H283" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I283" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J283" s="2" t="str">
         <x:v>active</x:v>
@@ -12501,7 +12501,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L283" s="14" t="str">
-        <x:v>2000-2024 拉萨市</x:v>
+        <x:v>1987-2026 拉萨市</x:v>
       </x:c>
       <x:c r="M283" s="15" t="str">
         <x:v>0</x:v>
@@ -12532,10 +12532,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H284" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I284" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J284" s="2" t="str">
         <x:v>active</x:v>
@@ -12544,7 +12544,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L284" s="14" t="str">
-        <x:v>2000-2013 日喀则地区; 2014-2024 日喀则市</x:v>
+        <x:v>1987-2013 日喀则地区; 2014-2026 日喀则市</x:v>
       </x:c>
       <x:c r="M284" s="15" t="str">
         <x:v>1</x:v>
@@ -12575,10 +12575,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H285" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I285" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J285" s="2" t="str">
         <x:v>active</x:v>
@@ -12587,7 +12587,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L285" s="14" t="str">
-        <x:v>2000-2013 昌都地区; 2014-2024 昌都市</x:v>
+        <x:v>1987-1999 昌都市; 2000-2013 昌都地区; 2014-2026 昌都市</x:v>
       </x:c>
       <x:c r="M285" s="15" t="str">
         <x:v>0</x:v>
@@ -12618,10 +12618,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H286" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I286" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J286" s="2" t="str">
         <x:v>active</x:v>
@@ -12630,7 +12630,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L286" s="14" t="str">
-        <x:v>2000-2014 林芝地区; 2015-2024 林芝市</x:v>
+        <x:v>1987-2014 林芝地区; 2015-2026 林芝市</x:v>
       </x:c>
       <x:c r="M286" s="15" t="str">
         <x:v>1</x:v>
@@ -12661,10 +12661,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H287" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I287" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J287" s="2" t="str">
         <x:v>active</x:v>
@@ -12673,7 +12673,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L287" s="14" t="str">
-        <x:v>2000-2015 山南地区; 2016-2024 山南市</x:v>
+        <x:v>1987-2015 山南地区; 2016-2026 山南市</x:v>
       </x:c>
       <x:c r="M287" s="15" t="str">
         <x:v>1</x:v>
@@ -12704,10 +12704,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H288" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I288" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J288" s="2" t="str">
         <x:v>active</x:v>
@@ -12716,7 +12716,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L288" s="14" t="str">
-        <x:v>2000-2016 那曲地区; 2017-2024 那曲市</x:v>
+        <x:v>1987-2016 那曲地区; 2017-2026 那曲市</x:v>
       </x:c>
       <x:c r="M288" s="15" t="str">
         <x:v>1</x:v>
@@ -12747,10 +12747,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H289" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I289" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J289" s="2" t="str">
         <x:v>active</x:v>
@@ -12759,7 +12759,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L289" s="14" t="str">
-        <x:v>2000-2024 阿里地区</x:v>
+        <x:v>1987-2026 阿里地区</x:v>
       </x:c>
       <x:c r="M289" s="15" t="str">
         <x:v>0</x:v>
@@ -12790,10 +12790,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H290" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I290" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J290" s="2" t="str">
         <x:v>active</x:v>
@@ -12802,7 +12802,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L290" s="14" t="str">
-        <x:v>2000-2024 西安市</x:v>
+        <x:v>1987-2026 西安市</x:v>
       </x:c>
       <x:c r="M290" s="15" t="str">
         <x:v>0</x:v>
@@ -12833,10 +12833,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H291" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I291" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J291" s="2" t="str">
         <x:v>active</x:v>
@@ -12845,7 +12845,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L291" s="14" t="str">
-        <x:v>2000-2024 铜川市</x:v>
+        <x:v>1987-2026 铜川市</x:v>
       </x:c>
       <x:c r="M291" s="15" t="str">
         <x:v>0</x:v>
@@ -12876,10 +12876,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H292" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I292" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J292" s="2" t="str">
         <x:v>active</x:v>
@@ -12888,7 +12888,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L292" s="14" t="str">
-        <x:v>2000-2024 宝鸡市</x:v>
+        <x:v>1987-2026 宝鸡市</x:v>
       </x:c>
       <x:c r="M292" s="15" t="str">
         <x:v>0</x:v>
@@ -12919,10 +12919,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H293" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I293" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J293" s="2" t="str">
         <x:v>active</x:v>
@@ -12931,7 +12931,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L293" s="14" t="str">
-        <x:v>2000-2024 咸阳市</x:v>
+        <x:v>1987-2026 咸阳市</x:v>
       </x:c>
       <x:c r="M293" s="15" t="str">
         <x:v>0</x:v>
@@ -12962,10 +12962,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H294" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I294" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J294" s="2" t="str">
         <x:v>active</x:v>
@@ -12974,7 +12974,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L294" s="14" t="str">
-        <x:v>2000-2024 渭南市</x:v>
+        <x:v>1987-1993 渭南地区; 1994-2026 渭南市</x:v>
       </x:c>
       <x:c r="M294" s="15" t="str">
         <x:v>1</x:v>
@@ -13005,10 +13005,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H295" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I295" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J295" s="2" t="str">
         <x:v>active</x:v>
@@ -13017,7 +13017,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L295" s="14" t="str">
-        <x:v>2000-2024 延安市</x:v>
+        <x:v>1987-1995 延安地区; 1996-2026 延安市</x:v>
       </x:c>
       <x:c r="M295" s="15" t="str">
         <x:v>1</x:v>
@@ -13048,10 +13048,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H296" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I296" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J296" s="2" t="str">
         <x:v>active</x:v>
@@ -13060,7 +13060,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L296" s="14" t="str">
-        <x:v>2000-2024 汉中市</x:v>
+        <x:v>1987-1995 汉中地区; 1996-2026 汉中市</x:v>
       </x:c>
       <x:c r="M296" s="15" t="str">
         <x:v>1</x:v>
@@ -13091,10 +13091,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H297" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I297" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J297" s="2" t="str">
         <x:v>active</x:v>
@@ -13103,7 +13103,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L297" s="14" t="str">
-        <x:v>2000-2024 榆林市</x:v>
+        <x:v>1987-1998 榆林地区; 1999-2026 榆林市</x:v>
       </x:c>
       <x:c r="M297" s="15" t="str">
         <x:v>1</x:v>
@@ -13134,10 +13134,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H298" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I298" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J298" s="2" t="str">
         <x:v>active</x:v>
@@ -13146,7 +13146,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L298" s="14" t="str">
-        <x:v>2000-2024 安康市</x:v>
+        <x:v>1987-1999 安康地区; 2000-2026 安康市</x:v>
       </x:c>
       <x:c r="M298" s="15" t="str">
         <x:v>1</x:v>
@@ -13177,10 +13177,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H299" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I299" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J299" s="2" t="str">
         <x:v>active</x:v>
@@ -13189,7 +13189,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L299" s="14" t="str">
-        <x:v>2000-2000 商洛地区; 2001-2024 商洛市</x:v>
+        <x:v>1987-2000 商洛地区; 2001-2026 商洛市</x:v>
       </x:c>
       <x:c r="M299" s="15" t="str">
         <x:v>1</x:v>
@@ -13220,10 +13220,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H300" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I300" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J300" s="2" t="str">
         <x:v>active</x:v>
@@ -13232,7 +13232,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L300" s="14" t="str">
-        <x:v>2000-2024 兰州市</x:v>
+        <x:v>1987-2026 兰州市</x:v>
       </x:c>
       <x:c r="M300" s="15" t="str">
         <x:v>0</x:v>
@@ -13263,10 +13263,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H301" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I301" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J301" s="2" t="str">
         <x:v>active</x:v>
@@ -13275,7 +13275,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L301" s="14" t="str">
-        <x:v>2000-2024 嘉峪关市</x:v>
+        <x:v>1987-2026 嘉峪关市</x:v>
       </x:c>
       <x:c r="M301" s="15" t="str">
         <x:v>0</x:v>
@@ -13306,10 +13306,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H302" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I302" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J302" s="2" t="str">
         <x:v>active</x:v>
@@ -13318,7 +13318,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L302" s="14" t="str">
-        <x:v>2000-2024 金昌市</x:v>
+        <x:v>1987-2026 金昌市</x:v>
       </x:c>
       <x:c r="M302" s="15" t="str">
         <x:v>0</x:v>
@@ -13349,10 +13349,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H303" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I303" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J303" s="2" t="str">
         <x:v>active</x:v>
@@ -13361,7 +13361,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L303" s="14" t="str">
-        <x:v>2000-2024 白银市</x:v>
+        <x:v>1987-2026 白银市</x:v>
       </x:c>
       <x:c r="M303" s="15" t="str">
         <x:v>0</x:v>
@@ -13392,10 +13392,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H304" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I304" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J304" s="2" t="str">
         <x:v>active</x:v>
@@ -13404,7 +13404,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L304" s="14" t="str">
-        <x:v>2000-2024 天水市</x:v>
+        <x:v>1987-2026 天水市</x:v>
       </x:c>
       <x:c r="M304" s="15" t="str">
         <x:v>0</x:v>
@@ -13435,10 +13435,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H305" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I305" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J305" s="2" t="str">
         <x:v>active</x:v>
@@ -13447,7 +13447,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L305" s="14" t="str">
-        <x:v>2000-2000 武威地区; 2001-2024 武威市</x:v>
+        <x:v>1987-2000 武威地区; 2001-2026 武威市</x:v>
       </x:c>
       <x:c r="M305" s="15" t="str">
         <x:v>1</x:v>
@@ -13478,10 +13478,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H306" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I306" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J306" s="2" t="str">
         <x:v>active</x:v>
@@ -13490,7 +13490,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L306" s="14" t="str">
-        <x:v>2000-2001 张掖地区; 2002-2024 张掖市</x:v>
+        <x:v>1987-2001 张掖地区; 2002-2026 张掖市</x:v>
       </x:c>
       <x:c r="M306" s="15" t="str">
         <x:v>1</x:v>
@@ -13521,10 +13521,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H307" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I307" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J307" s="2" t="str">
         <x:v>active</x:v>
@@ -13533,7 +13533,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L307" s="14" t="str">
-        <x:v>2000-2001 平凉地区; 2002-2024 平凉市</x:v>
+        <x:v>1987-2001 平凉地区; 2002-2026 平凉市</x:v>
       </x:c>
       <x:c r="M307" s="15" t="str">
         <x:v>1</x:v>
@@ -13564,10 +13564,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H308" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I308" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J308" s="2" t="str">
         <x:v>active</x:v>
@@ -13576,7 +13576,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L308" s="14" t="str">
-        <x:v>2000-2001 酒泉地区; 2002-2024 酒泉市</x:v>
+        <x:v>1987-2001 酒泉地区; 2002-2026 酒泉市</x:v>
       </x:c>
       <x:c r="M308" s="15" t="str">
         <x:v>1</x:v>
@@ -13607,10 +13607,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H309" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I309" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J309" s="2" t="str">
         <x:v>active</x:v>
@@ -13619,7 +13619,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L309" s="14" t="str">
-        <x:v>2000-2001 庆阳地区; 2002-2024 庆阳市</x:v>
+        <x:v>1987-2001 庆阳地区; 2002-2026 庆阳市</x:v>
       </x:c>
       <x:c r="M309" s="15" t="str">
         <x:v>1</x:v>
@@ -13650,10 +13650,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H310" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I310" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J310" s="2" t="str">
         <x:v>active</x:v>
@@ -13662,7 +13662,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L310" s="14" t="str">
-        <x:v>2000-2002 定西地区; 2003-2024 定西市</x:v>
+        <x:v>1987-2002 定西地区; 2003-2026 定西市</x:v>
       </x:c>
       <x:c r="M310" s="15" t="str">
         <x:v>1</x:v>
@@ -13693,10 +13693,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H311" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I311" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J311" s="2" t="str">
         <x:v>active</x:v>
@@ -13705,7 +13705,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L311" s="14" t="str">
-        <x:v>2000-2003 陇南地区; 2004-2024 陇南市</x:v>
+        <x:v>1987-2003 陇南地区; 2004-2026 陇南市</x:v>
       </x:c>
       <x:c r="M311" s="15" t="str">
         <x:v>1</x:v>
@@ -13736,10 +13736,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H312" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I312" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J312" s="2" t="str">
         <x:v>active</x:v>
@@ -13748,7 +13748,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L312" s="14" t="str">
-        <x:v>2000-2024 临夏回族自治州</x:v>
+        <x:v>1987-2026 临夏回族自治州</x:v>
       </x:c>
       <x:c r="M312" s="15" t="str">
         <x:v>0</x:v>
@@ -13779,10 +13779,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H313" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I313" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J313" s="2" t="str">
         <x:v>active</x:v>
@@ -13791,7 +13791,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L313" s="14" t="str">
-        <x:v>2000-2024 甘南藏族自治州</x:v>
+        <x:v>1987-2026 甘南藏族自治州</x:v>
       </x:c>
       <x:c r="M313" s="15" t="str">
         <x:v>0</x:v>
@@ -13822,10 +13822,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H314" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I314" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J314" s="2" t="str">
         <x:v>active</x:v>
@@ -13834,7 +13834,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L314" s="14" t="str">
-        <x:v>2000-2024 西宁市</x:v>
+        <x:v>1987-2026 西宁市</x:v>
       </x:c>
       <x:c r="M314" s="15" t="str">
         <x:v>0</x:v>
@@ -13865,10 +13865,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H315" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I315" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J315" s="2" t="str">
         <x:v>active</x:v>
@@ -13877,7 +13877,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L315" s="14" t="str">
-        <x:v>2000-2012 海东地区; 2013-2024 海东市</x:v>
+        <x:v>1987-2012 海东地区; 2013-2026 海东市</x:v>
       </x:c>
       <x:c r="M315" s="15" t="str">
         <x:v>1</x:v>
@@ -13908,10 +13908,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H316" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I316" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J316" s="2" t="str">
         <x:v>active</x:v>
@@ -13920,7 +13920,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L316" s="14" t="str">
-        <x:v>2000-2024 海北藏族自治州</x:v>
+        <x:v>1987-2026 海北藏族自治州</x:v>
       </x:c>
       <x:c r="M316" s="15" t="str">
         <x:v>0</x:v>
@@ -13951,10 +13951,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H317" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I317" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J317" s="2" t="str">
         <x:v>active</x:v>
@@ -13963,7 +13963,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L317" s="14" t="str">
-        <x:v>2000-2024 黄南藏族自治州</x:v>
+        <x:v>1987-2026 黄南藏族自治州</x:v>
       </x:c>
       <x:c r="M317" s="15" t="str">
         <x:v>0</x:v>
@@ -13994,10 +13994,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H318" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I318" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J318" s="2" t="str">
         <x:v>active</x:v>
@@ -14006,7 +14006,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L318" s="14" t="str">
-        <x:v>2000-2024 海南藏族自治州</x:v>
+        <x:v>1987-2026 海南藏族自治州</x:v>
       </x:c>
       <x:c r="M318" s="15" t="str">
         <x:v>0</x:v>
@@ -14037,10 +14037,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H319" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I319" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J319" s="2" t="str">
         <x:v>active</x:v>
@@ -14049,7 +14049,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L319" s="14" t="str">
-        <x:v>2000-2024 果洛藏族自治州</x:v>
+        <x:v>1987-2026 果洛藏族自治州</x:v>
       </x:c>
       <x:c r="M319" s="15" t="str">
         <x:v>0</x:v>
@@ -14080,10 +14080,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H320" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I320" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J320" s="2" t="str">
         <x:v>active</x:v>
@@ -14092,7 +14092,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L320" s="14" t="str">
-        <x:v>2000-2024 玉树藏族自治州</x:v>
+        <x:v>1987-2026 玉树藏族自治州</x:v>
       </x:c>
       <x:c r="M320" s="15" t="str">
         <x:v>0</x:v>
@@ -14123,10 +14123,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H321" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I321" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J321" s="2" t="str">
         <x:v>active</x:v>
@@ -14135,7 +14135,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L321" s="14" t="str">
-        <x:v>2000-2024 海西蒙古族藏族自治州</x:v>
+        <x:v>1987-2026 海西蒙古族藏族自治州</x:v>
       </x:c>
       <x:c r="M321" s="15" t="str">
         <x:v>0</x:v>
@@ -14166,10 +14166,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H322" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I322" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J322" s="2" t="str">
         <x:v>active</x:v>
@@ -14178,7 +14178,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L322" s="14" t="str">
-        <x:v>2000-2024 银川市</x:v>
+        <x:v>1987-2026 银川市</x:v>
       </x:c>
       <x:c r="M322" s="15" t="str">
         <x:v>0</x:v>
@@ -14209,10 +14209,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H323" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I323" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J323" s="2" t="str">
         <x:v>active</x:v>
@@ -14221,7 +14221,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L323" s="14" t="str">
-        <x:v>2000-2024 石嘴山市</x:v>
+        <x:v>1987-2026 石嘴山市</x:v>
       </x:c>
       <x:c r="M323" s="15" t="str">
         <x:v>0</x:v>
@@ -14252,10 +14252,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H324" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I324" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J324" s="2" t="str">
         <x:v>active</x:v>
@@ -14264,7 +14264,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L324" s="14" t="str">
-        <x:v>2000-2024 吴忠市</x:v>
+        <x:v>1987-1997 银南地区; 1998-2026 吴忠市</x:v>
       </x:c>
       <x:c r="M324" s="15" t="str">
         <x:v>1</x:v>
@@ -14295,10 +14295,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H325" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I325" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J325" s="2" t="str">
         <x:v>active</x:v>
@@ -14307,7 +14307,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L325" s="14" t="str">
-        <x:v>2000-2000 固原地区; 2001-2024 固原市</x:v>
+        <x:v>1987-2000 固原地区; 2001-2026 固原市</x:v>
       </x:c>
       <x:c r="M325" s="15" t="str">
         <x:v>1</x:v>
@@ -14341,7 +14341,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="I326" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J326" s="2" t="str">
         <x:v>active</x:v>
@@ -14350,7 +14350,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L326" s="14" t="str">
-        <x:v>2000-2002 [not_established]; 2003-2024 中卫市</x:v>
+        <x:v>1987-1999 [not_established]; 2000-2002 [not_established]; 2003-2026 中卫市</x:v>
       </x:c>
       <x:c r="M326" s="15" t="str">
         <x:v>1</x:v>
@@ -14381,10 +14381,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H327" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I327" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J327" s="2" t="str">
         <x:v>active</x:v>
@@ -14393,7 +14393,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L327" s="14" t="str">
-        <x:v>2000-2024 乌鲁木齐市</x:v>
+        <x:v>1987-2026 乌鲁木齐市</x:v>
       </x:c>
       <x:c r="M327" s="15" t="str">
         <x:v>0</x:v>
@@ -14424,10 +14424,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H328" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I328" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J328" s="2" t="str">
         <x:v>active</x:v>
@@ -14436,7 +14436,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L328" s="14" t="str">
-        <x:v>2000-2024 克拉玛依市</x:v>
+        <x:v>1987-2026 克拉玛依市</x:v>
       </x:c>
       <x:c r="M328" s="15" t="str">
         <x:v>0</x:v>
@@ -14467,10 +14467,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H329" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I329" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J329" s="2" t="str">
         <x:v>active</x:v>
@@ -14479,7 +14479,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L329" s="14" t="str">
-        <x:v>2000-2014 吐鲁番地区; 2015-2024 吐鲁番市</x:v>
+        <x:v>1987-2014 吐鲁番地区; 2015-2026 吐鲁番市</x:v>
       </x:c>
       <x:c r="M329" s="15" t="str">
         <x:v>1</x:v>
@@ -14510,10 +14510,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H330" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I330" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J330" s="2" t="str">
         <x:v>active</x:v>
@@ -14522,7 +14522,7 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L330" s="14" t="str">
-        <x:v>2000-2015 哈密地区; 2016-2024 哈密市</x:v>
+        <x:v>1987-2015 哈密地区; 2016-2026 哈密市</x:v>
       </x:c>
       <x:c r="M330" s="15" t="str">
         <x:v>1</x:v>
@@ -14553,10 +14553,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H331" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I331" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J331" s="2" t="str">
         <x:v>active</x:v>
@@ -14565,7 +14565,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L331" s="14" t="str">
-        <x:v>2000-2024 昌吉回族自治州</x:v>
+        <x:v>1987-2026 昌吉回族自治州</x:v>
       </x:c>
       <x:c r="M331" s="15" t="str">
         <x:v>0</x:v>
@@ -14596,10 +14596,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H332" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I332" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J332" s="2" t="str">
         <x:v>active</x:v>
@@ -14608,7 +14608,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L332" s="14" t="str">
-        <x:v>2000-2024 博尔塔拉蒙古自治州</x:v>
+        <x:v>1987-2026 博尔塔拉蒙古自治州</x:v>
       </x:c>
       <x:c r="M332" s="15" t="str">
         <x:v>0</x:v>
@@ -14639,10 +14639,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H333" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I333" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J333" s="2" t="str">
         <x:v>active</x:v>
@@ -14651,7 +14651,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L333" s="14" t="str">
-        <x:v>2000-2024 巴音郭楞蒙古自治州</x:v>
+        <x:v>1987-2026 巴音郭楞蒙古自治州</x:v>
       </x:c>
       <x:c r="M333" s="15" t="str">
         <x:v>0</x:v>
@@ -14682,10 +14682,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H334" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I334" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J334" s="2" t="str">
         <x:v>active</x:v>
@@ -14694,7 +14694,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L334" s="14" t="str">
-        <x:v>2000-2024 阿克苏地区</x:v>
+        <x:v>1987-2026 阿克苏地区</x:v>
       </x:c>
       <x:c r="M334" s="15" t="str">
         <x:v>0</x:v>
@@ -14725,10 +14725,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H335" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I335" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J335" s="2" t="str">
         <x:v>active</x:v>
@@ -14737,7 +14737,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L335" s="14" t="str">
-        <x:v>2000-2024 克孜勒苏柯尔克孜自治州</x:v>
+        <x:v>1987-2026 克孜勒苏柯尔克孜自治州</x:v>
       </x:c>
       <x:c r="M335" s="15" t="str">
         <x:v>0</x:v>
@@ -14768,10 +14768,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H336" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I336" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J336" s="2" t="str">
         <x:v>active</x:v>
@@ -14780,7 +14780,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L336" s="14" t="str">
-        <x:v>2000-2024 喀什地区</x:v>
+        <x:v>1987-2026 喀什地区</x:v>
       </x:c>
       <x:c r="M336" s="15" t="str">
         <x:v>0</x:v>
@@ -14811,10 +14811,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H337" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I337" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J337" s="2" t="str">
         <x:v>active</x:v>
@@ -14823,7 +14823,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L337" s="14" t="str">
-        <x:v>2000-2024 和田地区</x:v>
+        <x:v>1987-2026 和田地区</x:v>
       </x:c>
       <x:c r="M337" s="15" t="str">
         <x:v>0</x:v>
@@ -14854,10 +14854,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H338" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I338" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J338" s="2" t="str">
         <x:v>active</x:v>
@@ -14866,7 +14866,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L338" s="14" t="str">
-        <x:v>2000-2024 伊犁哈萨克自治州</x:v>
+        <x:v>1987-2026 伊犁哈萨克自治州</x:v>
       </x:c>
       <x:c r="M338" s="15" t="str">
         <x:v>0</x:v>
@@ -14897,7 +14897,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H339" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I339" s="12" t="str">
         <x:v>2000</x:v>
@@ -14909,7 +14909,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L339" s="14" t="str">
-        <x:v>2000-2000 伊犁地区; 2001-2024 [abolished]</x:v>
+        <x:v>1987-2000 伊犁地区; 2001-2026 [abolished]</x:v>
       </x:c>
       <x:c r="M339" s="15" t="str">
         <x:v>1</x:v>
@@ -14940,10 +14940,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H340" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I340" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J340" s="2" t="str">
         <x:v>active</x:v>
@@ -14952,7 +14952,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L340" s="14" t="str">
-        <x:v>2000-2024 塔城地区</x:v>
+        <x:v>1987-2026 塔城地区</x:v>
       </x:c>
       <x:c r="M340" s="15" t="str">
         <x:v>0</x:v>
@@ -14983,10 +14983,10 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H341" s="12" t="str">
-        <x:v>2000</x:v>
+        <x:v>1987</x:v>
       </x:c>
       <x:c r="I341" s="12" t="str">
-        <x:v>2024</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="J341" s="2" t="str">
         <x:v>active</x:v>
@@ -14995,7 +14995,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L341" s="14" t="str">
-        <x:v>2000-2024 阿勒泰地区</x:v>
+        <x:v>1987-2026 阿勒泰地区</x:v>
       </x:c>
       <x:c r="M341" s="15" t="str">
         <x:v>0</x:v>
@@ -15241,7 +15241,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0053b0f68db24f7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdba77a3c4a34037"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/releases/v2.0/china_city_entity_master_V2.0.xlsx
+++ b/data/releases/v2.0/china_city_entity_master_V2.0.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市总表" sheetId="1" r:id="R6849269ba1a643d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市总表" sheetId="1" r:id="R72f66fb9520143c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4018,7 +4018,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H86" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1996</x:v>
       </x:c>
       <x:c r="I86" s="12" t="str">
         <x:v>2026</x:v>
@@ -4030,7 +4030,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L86" s="14" t="str">
-        <x:v>1987-2026 泰州市</x:v>
+        <x:v>1987-1995 [not_established]; 1996-2026 泰州市</x:v>
       </x:c>
       <x:c r="M86" s="15" t="str">
         <x:v>0</x:v>
@@ -4061,7 +4061,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H87" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1996</x:v>
       </x:c>
       <x:c r="I87" s="12" t="str">
         <x:v>2026</x:v>
@@ -4073,7 +4073,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L87" s="14" t="str">
-        <x:v>1987-2026 宿迁市</x:v>
+        <x:v>1987-1995 [not_established]; 1996-2026 宿迁市</x:v>
       </x:c>
       <x:c r="M87" s="15" t="str">
         <x:v>0</x:v>
@@ -9221,7 +9221,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H207" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I207" s="12" t="str">
         <x:v>2026</x:v>
@@ -9233,10 +9233,10 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L207" s="14" t="str">
-        <x:v>1987-1987 惠阳地区; 1988-2026 惠州市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 惠州市</x:v>
       </x:c>
       <x:c r="M207" s="15" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N207" s="14" t="str"/>
       <x:c r="O207" s="14" t="str"/>
@@ -10253,7 +10253,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H231" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>2002</x:v>
       </x:c>
       <x:c r="I231" s="12" t="str">
         <x:v>2026</x:v>
@@ -10262,13 +10262,13 @@
         <x:v>active</x:v>
       </x:c>
       <x:c r="K231" s="2" t="str">
-        <x:v>event_crosschecked</x:v>
+        <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L231" s="14" t="str">
-        <x:v>1987-2001 南宁地区; 2002-2026 崇左市</x:v>
+        <x:v>1987-2001 [not_established]; 2002-2026 崇左市</x:v>
       </x:c>
       <x:c r="M231" s="15" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N231" s="14" t="str"/>
       <x:c r="O231" s="14" t="str"/>
@@ -10394,7 +10394,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L234" s="14" t="str">
-        <x:v>1987-1999 [not_established]; 2000-2011 [not_established]; 2012-2026 三沙市</x:v>
+        <x:v>1987-2011 [not_established]; 2012-2026 三沙市</x:v>
       </x:c>
       <x:c r="M234" s="15" t="str">
         <x:v>1</x:v>
@@ -14350,7 +14350,7 @@
         <x:v>wikipedia_verified</x:v>
       </x:c>
       <x:c r="L326" s="14" t="str">
-        <x:v>1987-1999 [not_established]; 2000-2002 [not_established]; 2003-2026 中卫市</x:v>
+        <x:v>1987-2002 [not_established]; 2003-2026 中卫市</x:v>
       </x:c>
       <x:c r="M326" s="15" t="str">
         <x:v>1</x:v>
@@ -15123,7 +15123,7 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="I344" s="12" t="str">
-        <x:v>1993</x:v>
+        <x:v>1992</x:v>
       </x:c>
       <x:c r="J344" s="2" t="str">
         <x:v>abolished</x:v>
@@ -15132,7 +15132,7 @@
         <x:v>reviewed</x:v>
       </x:c>
       <x:c r="L344" s="14" t="str">
-        <x:v>1970-1993 雁北地区</x:v>
+        <x:v>1970-1992 雁北地区</x:v>
       </x:c>
       <x:c r="M344" s="15" t="str">
         <x:v>1</x:v>
@@ -15238,10 +15238,104 @@
         <x:v>https://zh.wikipedia.org/wiki/黔江地区</x:v>
       </x:c>
     </x:row>
+    <x:row r="347" ht="20" customHeight="1">
+      <x:c r="A347" s="2" t="str">
+        <x:v>CNUR-000346</x:v>
+      </x:c>
+      <x:c r="B347" s="2" t="str">
+        <x:v>HIST-GX-NANNING</x:v>
+      </x:c>
+      <x:c r="C347" s="2" t="str">
+        <x:v>南宁地区</x:v>
+      </x:c>
+      <x:c r="D347" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E347" s="2" t="str">
+        <x:v>广西壮族自治区</x:v>
+      </x:c>
+      <x:c r="F347" s="2" t="str">
+        <x:v>广西</x:v>
+      </x:c>
+      <x:c r="G347" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H347" s="2" t="str">
+        <x:v>1971</x:v>
+      </x:c>
+      <x:c r="I347" s="2" t="str">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="J347" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K347" s="2" t="str">
+        <x:v>reviewed_county_composition</x:v>
+      </x:c>
+      <x:c r="L347" s="2" t="str">
+        <x:v>1971-2001 南宁地区</x:v>
+      </x:c>
+      <x:c r="M347" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N347" s="2" t="str">
+        <x:v>撤销后主要分为崇左市并将五县划归南宁市</x:v>
+      </x:c>
+      <x:c r="O347" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/南宁地区</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="20" customHeight="1">
+      <x:c r="A348" s="2" t="str">
+        <x:v>CNUR-000347</x:v>
+      </x:c>
+      <x:c r="B348" s="2" t="str">
+        <x:v>HIST-GD-HUIYANG</x:v>
+      </x:c>
+      <x:c r="C348" s="2" t="str">
+        <x:v>惠阳地区</x:v>
+      </x:c>
+      <x:c r="D348" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E348" s="2" t="str">
+        <x:v>广东省</x:v>
+      </x:c>
+      <x:c r="F348" s="2" t="str">
+        <x:v>广东</x:v>
+      </x:c>
+      <x:c r="G348" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H348" s="2" t="str">
+        <x:v>1970</x:v>
+      </x:c>
+      <x:c r="I348" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="J348" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K348" s="2" t="str">
+        <x:v>reviewed_county_composition</x:v>
+      </x:c>
+      <x:c r="L348" s="2" t="str">
+        <x:v>1970-1987 惠阳地区</x:v>
+      </x:c>
+      <x:c r="M348" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N348" s="2" t="str">
+        <x:v>撤销后主要形成惠州市、汕尾市和河源市</x:v>
+      </x:c>
+      <x:c r="O348" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/惠阳地区</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdba77a3c4a34037"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01aebbe0ea2a43fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/releases/v2.0/china_city_entity_master_V2.0.xlsx
+++ b/data/releases/v2.0/china_city_entity_master_V2.0.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市总表" sheetId="1" r:id="R72f66fb9520143c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市总表" sheetId="1" r:id="R8e85c665558844e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -507,7 +507,7 @@
         <x:v>1987-2026 石家庄市</x:v>
       </x:c>
       <x:c r="M4" s="15" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N4" s="14" t="str"/>
       <x:c r="O4" s="14" t="str"/>
@@ -4893,7 +4893,7 @@
         <x:v>1987-2026 安庆市</x:v>
       </x:c>
       <x:c r="M106" s="15" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N106" s="14" t="str"/>
       <x:c r="O106" s="14" t="str"/>
@@ -6598,7 +6598,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H146" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1989</x:v>
       </x:c>
       <x:c r="I146" s="12" t="str">
         <x:v>2026</x:v>
@@ -6610,7 +6610,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L146" s="14" t="str">
-        <x:v>1987-2026 日照市</x:v>
+        <x:v>1987-1988 [not_established]; 1989-2026 日照市</x:v>
       </x:c>
       <x:c r="M146" s="15" t="str">
         <x:v>0</x:v>
@@ -7731,7 +7731,7 @@
         <x:v>1987-2026 十堰市</x:v>
       </x:c>
       <x:c r="M172" s="15" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N172" s="14" t="str"/>
       <x:c r="O172" s="14" t="str"/>
@@ -7774,7 +7774,7 @@
         <x:v>1987-2026 宜昌市</x:v>
       </x:c>
       <x:c r="M173" s="15" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N173" s="14" t="str"/>
       <x:c r="O173" s="14" t="str"/>
@@ -7974,7 +7974,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H178" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1994</x:v>
       </x:c>
       <x:c r="I178" s="12" t="str">
         <x:v>2026</x:v>
@@ -7986,10 +7986,10 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L178" s="14" t="str">
-        <x:v>1987-1993 荆州地区; 1994-1995 荆沙市; 1996-2026 荆州市</x:v>
+        <x:v>1987-1993 [not_established]; 1994-1995 荆沙市; 1996-2026 荆州市</x:v>
       </x:c>
       <x:c r="M178" s="15" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N178" s="14" t="str"/>
       <x:c r="O178" s="14" t="str"/>
@@ -8490,7 +8490,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H190" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I190" s="12" t="str">
         <x:v>2026</x:v>
@@ -8502,7 +8502,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L190" s="14" t="str">
-        <x:v>1987-1993 大庸市; 1994-2026 张家界市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-1993 大庸市; 1994-2026 张家界市</x:v>
       </x:c>
       <x:c r="M190" s="15" t="str">
         <x:v>1</x:v>
@@ -9479,7 +9479,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H213" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I213" s="12" t="str">
         <x:v>2026</x:v>
@@ -9491,7 +9491,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L213" s="14" t="str">
-        <x:v>1987-2026 东莞市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 东莞市</x:v>
       </x:c>
       <x:c r="M213" s="15" t="str">
         <x:v>0</x:v>
@@ -9522,7 +9522,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H214" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I214" s="12" t="str">
         <x:v>2026</x:v>
@@ -9534,7 +9534,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L214" s="14" t="str">
-        <x:v>1987-2026 中山市</x:v>
+        <x:v>1987-1987 [not_established]; 1988-2026 中山市</x:v>
       </x:c>
       <x:c r="M214" s="15" t="str">
         <x:v>0</x:v>
@@ -9565,7 +9565,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H215" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1991</x:v>
       </x:c>
       <x:c r="I215" s="12" t="str">
         <x:v>2026</x:v>
@@ -9577,7 +9577,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L215" s="14" t="str">
-        <x:v>1987-2026 潮州市</x:v>
+        <x:v>1987-1990 [not_established]; 1991-2026 潮州市</x:v>
       </x:c>
       <x:c r="M215" s="15" t="str">
         <x:v>0</x:v>
@@ -9608,7 +9608,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H216" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1991</x:v>
       </x:c>
       <x:c r="I216" s="12" t="str">
         <x:v>2026</x:v>
@@ -9620,7 +9620,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L216" s="14" t="str">
-        <x:v>1987-2026 揭阳市</x:v>
+        <x:v>1987-1990 [not_established]; 1991-2026 揭阳市</x:v>
       </x:c>
       <x:c r="M216" s="15" t="str">
         <x:v>0</x:v>
@@ -9651,7 +9651,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H217" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1994</x:v>
       </x:c>
       <x:c r="I217" s="12" t="str">
         <x:v>2026</x:v>
@@ -9663,7 +9663,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L217" s="14" t="str">
-        <x:v>1987-2026 云浮市</x:v>
+        <x:v>1987-1993 [not_established]; 1994-2026 云浮市</x:v>
       </x:c>
       <x:c r="M217" s="15" t="str">
         <x:v>0</x:v>
@@ -9995,7 +9995,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H225" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1995</x:v>
       </x:c>
       <x:c r="I225" s="12" t="str">
         <x:v>2026</x:v>
@@ -10007,7 +10007,7 @@
         <x:v>wikipedia_entity_verified</x:v>
       </x:c>
       <x:c r="L225" s="14" t="str">
-        <x:v>1987-2026 贵港市</x:v>
+        <x:v>1987-1994 [not_established]; 1995-2026 贵港市</x:v>
       </x:c>
       <x:c r="M225" s="15" t="str">
         <x:v>0</x:v>
@@ -10124,7 +10124,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H228" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>1997</x:v>
       </x:c>
       <x:c r="I228" s="12" t="str">
         <x:v>2026</x:v>
@@ -10136,10 +10136,10 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L228" s="14" t="str">
-        <x:v>1987-1996 梧州地区; 1997-2001 贺州地区; 2002-2026 贺州市</x:v>
+        <x:v>1987-1996 [not_established]; 1997-2001 贺州地区; 2002-2026 贺州市</x:v>
       </x:c>
       <x:c r="M228" s="15" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N228" s="14" t="str"/>
       <x:c r="O228" s="14" t="str"/>
@@ -10210,7 +10210,7 @@
         <x:v>prefecture_research_entity</x:v>
       </x:c>
       <x:c r="H230" s="12" t="str">
-        <x:v>1987</x:v>
+        <x:v>2002</x:v>
       </x:c>
       <x:c r="I230" s="12" t="str">
         <x:v>2026</x:v>
@@ -10222,10 +10222,10 @@
         <x:v>event_crosschecked</x:v>
       </x:c>
       <x:c r="L230" s="14" t="str">
-        <x:v>1987-2001 柳州地区; 2002-2026 来宾市</x:v>
+        <x:v>1987-2001 [not_established]; 2002-2026 来宾市</x:v>
       </x:c>
       <x:c r="M230" s="15" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N230" s="14" t="str"/>
       <x:c r="O230" s="14" t="str"/>
@@ -15332,10 +15332,762 @@
         <x:v>https://zh.wikipedia.org/wiki/惠阳地区</x:v>
       </x:c>
     </x:row>
+    <x:row r="349" ht="20" customHeight="1">
+      <x:c r="A349" s="2" t="str">
+        <x:v>CNUR-000348</x:v>
+      </x:c>
+      <x:c r="B349" s="2" t="str">
+        <x:v>HIST-AH-ANQING</x:v>
+      </x:c>
+      <x:c r="C349" s="2" t="str">
+        <x:v>安庆地区</x:v>
+      </x:c>
+      <x:c r="D349" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E349" s="2" t="str">
+        <x:v>安徽省</x:v>
+      </x:c>
+      <x:c r="F349" s="2" t="str">
+        <x:v>安徽</x:v>
+      </x:c>
+      <x:c r="G349" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H349" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I349" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="J349" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K349" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L349" s="2" t="str">
+        <x:v>1987-1987 安庆地区</x:v>
+      </x:c>
+      <x:c r="M349" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N349" s="2" t="str">
+        <x:v>与既有安庆市合并并析设池州地区</x:v>
+      </x:c>
+      <x:c r="O349" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1988年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" ht="20" customHeight="1">
+      <x:c r="A350" s="2" t="str">
+        <x:v>CNUR-000349</x:v>
+      </x:c>
+      <x:c r="B350" s="2" t="str">
+        <x:v>HIST-HB-YICHANG</x:v>
+      </x:c>
+      <x:c r="C350" s="2" t="str">
+        <x:v>宜昌地区</x:v>
+      </x:c>
+      <x:c r="D350" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E350" s="2" t="str">
+        <x:v>湖北省</x:v>
+      </x:c>
+      <x:c r="F350" s="2" t="str">
+        <x:v>湖北</x:v>
+      </x:c>
+      <x:c r="G350" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H350" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I350" s="2" t="str">
+        <x:v>1991</x:v>
+      </x:c>
+      <x:c r="J350" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K350" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L350" s="2" t="str">
+        <x:v>1987-1991 宜昌地区</x:v>
+      </x:c>
+      <x:c r="M350" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N350" s="2" t="str">
+        <x:v>撤销后整体并入既有宜昌市</x:v>
+      </x:c>
+      <x:c r="O350" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1992年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="20" customHeight="1">
+      <x:c r="A351" s="2" t="str">
+        <x:v>CNUR-000350</x:v>
+      </x:c>
+      <x:c r="B351" s="2" t="str">
+        <x:v>HIST-HE-SHIJIAZHUANG</x:v>
+      </x:c>
+      <x:c r="C351" s="2" t="str">
+        <x:v>石家庄地区</x:v>
+      </x:c>
+      <x:c r="D351" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E351" s="2" t="str">
+        <x:v>河北省</x:v>
+      </x:c>
+      <x:c r="F351" s="2" t="str">
+        <x:v>河北</x:v>
+      </x:c>
+      <x:c r="G351" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H351" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I351" s="2" t="str">
+        <x:v>1992</x:v>
+      </x:c>
+      <x:c r="J351" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K351" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L351" s="2" t="str">
+        <x:v>1987-1992 石家庄地区</x:v>
+      </x:c>
+      <x:c r="M351" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N351" s="2" t="str">
+        <x:v>与既有石家庄市实行地市合并</x:v>
+      </x:c>
+      <x:c r="O351" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1993年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" ht="20" customHeight="1">
+      <x:c r="A352" s="2" t="str">
+        <x:v>CNUR-000351</x:v>
+      </x:c>
+      <x:c r="B352" s="2" t="str">
+        <x:v>HIST-HE-ZHANGJIAKOU</x:v>
+      </x:c>
+      <x:c r="C352" s="2" t="str">
+        <x:v>张家口地区</x:v>
+      </x:c>
+      <x:c r="D352" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E352" s="2" t="str">
+        <x:v>河北省</x:v>
+      </x:c>
+      <x:c r="F352" s="2" t="str">
+        <x:v>河北</x:v>
+      </x:c>
+      <x:c r="G352" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H352" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I352" s="2" t="str">
+        <x:v>1992</x:v>
+      </x:c>
+      <x:c r="J352" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K352" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L352" s="2" t="str">
+        <x:v>1987-1992 张家口地区</x:v>
+      </x:c>
+      <x:c r="M352" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N352" s="2" t="str">
+        <x:v>与既有张家口市实行地市合并</x:v>
+      </x:c>
+      <x:c r="O352" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1993年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="20" customHeight="1">
+      <x:c r="A353" s="2" t="str">
+        <x:v>CNUR-000352</x:v>
+      </x:c>
+      <x:c r="B353" s="2" t="str">
+        <x:v>HIST-HE-CANGZHOU</x:v>
+      </x:c>
+      <x:c r="C353" s="2" t="str">
+        <x:v>沧州地区</x:v>
+      </x:c>
+      <x:c r="D353" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E353" s="2" t="str">
+        <x:v>河北省</x:v>
+      </x:c>
+      <x:c r="F353" s="2" t="str">
+        <x:v>河北</x:v>
+      </x:c>
+      <x:c r="G353" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H353" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I353" s="2" t="str">
+        <x:v>1992</x:v>
+      </x:c>
+      <x:c r="J353" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K353" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L353" s="2" t="str">
+        <x:v>1987-1992 沧州地区</x:v>
+      </x:c>
+      <x:c r="M353" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N353" s="2" t="str">
+        <x:v>与既有沧州市实行地市合并</x:v>
+      </x:c>
+      <x:c r="O353" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1993年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" ht="20" customHeight="1">
+      <x:c r="A354" s="2" t="str">
+        <x:v>CNUR-000353</x:v>
+      </x:c>
+      <x:c r="B354" s="2" t="str">
+        <x:v>HIST-HE-HANDAN</x:v>
+      </x:c>
+      <x:c r="C354" s="2" t="str">
+        <x:v>邯郸地区</x:v>
+      </x:c>
+      <x:c r="D354" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E354" s="2" t="str">
+        <x:v>河北省</x:v>
+      </x:c>
+      <x:c r="F354" s="2" t="str">
+        <x:v>河北</x:v>
+      </x:c>
+      <x:c r="G354" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H354" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I354" s="2" t="str">
+        <x:v>1992</x:v>
+      </x:c>
+      <x:c r="J354" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K354" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L354" s="2" t="str">
+        <x:v>1987-1992 邯郸地区</x:v>
+      </x:c>
+      <x:c r="M354" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N354" s="2" t="str">
+        <x:v>与既有邯郸市实行地市合并</x:v>
+      </x:c>
+      <x:c r="O354" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1993年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="20" customHeight="1">
+      <x:c r="A355" s="2" t="str">
+        <x:v>CNUR-000354</x:v>
+      </x:c>
+      <x:c r="B355" s="2" t="str">
+        <x:v>HIST-HE-XINGTAI</x:v>
+      </x:c>
+      <x:c r="C355" s="2" t="str">
+        <x:v>邢台地区</x:v>
+      </x:c>
+      <x:c r="D355" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E355" s="2" t="str">
+        <x:v>河北省</x:v>
+      </x:c>
+      <x:c r="F355" s="2" t="str">
+        <x:v>河北</x:v>
+      </x:c>
+      <x:c r="G355" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H355" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I355" s="2" t="str">
+        <x:v>1992</x:v>
+      </x:c>
+      <x:c r="J355" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K355" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L355" s="2" t="str">
+        <x:v>1987-1992 邢台地区</x:v>
+      </x:c>
+      <x:c r="M355" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N355" s="2" t="str">
+        <x:v>与既有邢台市实行地市合并</x:v>
+      </x:c>
+      <x:c r="O355" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1993年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="20" customHeight="1">
+      <x:c r="A356" s="2" t="str">
+        <x:v>CNUR-000355</x:v>
+      </x:c>
+      <x:c r="B356" s="2" t="str">
+        <x:v>HIST-HE-CHENGDE</x:v>
+      </x:c>
+      <x:c r="C356" s="2" t="str">
+        <x:v>承德地区</x:v>
+      </x:c>
+      <x:c r="D356" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E356" s="2" t="str">
+        <x:v>河北省</x:v>
+      </x:c>
+      <x:c r="F356" s="2" t="str">
+        <x:v>河北</x:v>
+      </x:c>
+      <x:c r="G356" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H356" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I356" s="2" t="str">
+        <x:v>1992</x:v>
+      </x:c>
+      <x:c r="J356" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K356" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L356" s="2" t="str">
+        <x:v>1987-1992 承德地区</x:v>
+      </x:c>
+      <x:c r="M356" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N356" s="2" t="str">
+        <x:v>与既有承德市实行地市合并</x:v>
+      </x:c>
+      <x:c r="O356" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1993年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="20" customHeight="1">
+      <x:c r="A357" s="2" t="str">
+        <x:v>CNUR-000356</x:v>
+      </x:c>
+      <x:c r="B357" s="2" t="str">
+        <x:v>HIST-HE-BAODING</x:v>
+      </x:c>
+      <x:c r="C357" s="2" t="str">
+        <x:v>保定地区</x:v>
+      </x:c>
+      <x:c r="D357" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E357" s="2" t="str">
+        <x:v>河北省</x:v>
+      </x:c>
+      <x:c r="F357" s="2" t="str">
+        <x:v>河北</x:v>
+      </x:c>
+      <x:c r="G357" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H357" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I357" s="2" t="str">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c r="J357" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K357" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L357" s="2" t="str">
+        <x:v>1987-1993 保定地区</x:v>
+      </x:c>
+      <x:c r="M357" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N357" s="2" t="str">
+        <x:v>与既有保定市合并组建新的保定市</x:v>
+      </x:c>
+      <x:c r="O357" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1994年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="20" customHeight="1">
+      <x:c r="A358" s="2" t="str">
+        <x:v>CNUR-000357</x:v>
+      </x:c>
+      <x:c r="B358" s="2" t="str">
+        <x:v>HIST-HB-YUNYANG</x:v>
+      </x:c>
+      <x:c r="C358" s="2" t="str">
+        <x:v>郧阳地区</x:v>
+      </x:c>
+      <x:c r="D358" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E358" s="2" t="str">
+        <x:v>湖北省</x:v>
+      </x:c>
+      <x:c r="F358" s="2" t="str">
+        <x:v>湖北</x:v>
+      </x:c>
+      <x:c r="G358" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H358" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I358" s="2" t="str">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c r="J358" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K358" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L358" s="2" t="str">
+        <x:v>1987-1993 郧阳地区</x:v>
+      </x:c>
+      <x:c r="M358" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N358" s="2" t="str">
+        <x:v>撤销后与既有十堰市合并</x:v>
+      </x:c>
+      <x:c r="O358" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1994年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="20" customHeight="1">
+      <x:c r="A359" s="2" t="str">
+        <x:v>CNUR-000358</x:v>
+      </x:c>
+      <x:c r="B359" s="2" t="str">
+        <x:v>HIST-HB-JINGZHOU</x:v>
+      </x:c>
+      <x:c r="C359" s="2" t="str">
+        <x:v>荆州地区</x:v>
+      </x:c>
+      <x:c r="D359" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E359" s="2" t="str">
+        <x:v>湖北省</x:v>
+      </x:c>
+      <x:c r="F359" s="2" t="str">
+        <x:v>湖北</x:v>
+      </x:c>
+      <x:c r="G359" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H359" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I359" s="2" t="str">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c r="J359" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K359" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L359" s="2" t="str">
+        <x:v>1987-1993 荆州地区</x:v>
+      </x:c>
+      <x:c r="M359" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N359" s="2" t="str">
+        <x:v>与原地级沙市市共同组建荆沙市</x:v>
+      </x:c>
+      <x:c r="O359" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1994年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" ht="20" customHeight="1">
+      <x:c r="A360" s="2" t="str">
+        <x:v>CNUR-000359</x:v>
+      </x:c>
+      <x:c r="B360" s="2" t="str">
+        <x:v>HIST-HB-SHASHI</x:v>
+      </x:c>
+      <x:c r="C360" s="2" t="str">
+        <x:v>沙市市</x:v>
+      </x:c>
+      <x:c r="D360" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E360" s="2" t="str">
+        <x:v>湖北省</x:v>
+      </x:c>
+      <x:c r="F360" s="2" t="str">
+        <x:v>湖北</x:v>
+      </x:c>
+      <x:c r="G360" s="2" t="str">
+        <x:v>abolished_prefecture_level_city</x:v>
+      </x:c>
+      <x:c r="H360" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I360" s="2" t="str">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c r="J360" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K360" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L360" s="2" t="str">
+        <x:v>1987-1993 沙市市</x:v>
+      </x:c>
+      <x:c r="M360" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N360" s="2" t="str">
+        <x:v>与荆州地区共同组建荆沙市</x:v>
+      </x:c>
+      <x:c r="O360" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1994年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="20" customHeight="1">
+      <x:c r="A361" s="2" t="str">
+        <x:v>CNUR-000360</x:v>
+      </x:c>
+      <x:c r="B361" s="2" t="str">
+        <x:v>HIST-HLJ-SONGHUAJIANG</x:v>
+      </x:c>
+      <x:c r="C361" s="2" t="str">
+        <x:v>松花江地区</x:v>
+      </x:c>
+      <x:c r="D361" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E361" s="2" t="str">
+        <x:v>黑龙江省</x:v>
+      </x:c>
+      <x:c r="F361" s="2" t="str">
+        <x:v>黑龙江</x:v>
+      </x:c>
+      <x:c r="G361" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H361" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I361" s="2" t="str">
+        <x:v>1995</x:v>
+      </x:c>
+      <x:c r="J361" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K361" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L361" s="2" t="str">
+        <x:v>1987-1995 松花江地区</x:v>
+      </x:c>
+      <x:c r="M361" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N361" s="2" t="str">
+        <x:v>与既有哈尔滨市合并</x:v>
+      </x:c>
+      <x:c r="O361" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1996年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" ht="20" customHeight="1">
+      <x:c r="A362" s="2" t="str">
+        <x:v>CNUR-000361</x:v>
+      </x:c>
+      <x:c r="B362" s="2" t="str">
+        <x:v>HIST-GX-GUILIN</x:v>
+      </x:c>
+      <x:c r="C362" s="2" t="str">
+        <x:v>桂林地区</x:v>
+      </x:c>
+      <x:c r="D362" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E362" s="2" t="str">
+        <x:v>广西壮族自治区</x:v>
+      </x:c>
+      <x:c r="F362" s="2" t="str">
+        <x:v>广西</x:v>
+      </x:c>
+      <x:c r="G362" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H362" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I362" s="2" t="str">
+        <x:v>1997</x:v>
+      </x:c>
+      <x:c r="J362" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K362" s="2" t="str">
+        <x:v>reviewed_event_row</x:v>
+      </x:c>
+      <x:c r="L362" s="2" t="str">
+        <x:v>1987-1997 桂林地区</x:v>
+      </x:c>
+      <x:c r="M362" s="2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N362" s="2" t="str">
+        <x:v>与既有桂林市合并</x:v>
+      </x:c>
+      <x:c r="O362" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1998年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="20" customHeight="1">
+      <x:c r="A363" s="2" t="str">
+        <x:v>CNUR-000362</x:v>
+      </x:c>
+      <x:c r="B363" s="2" t="str">
+        <x:v>HIST-GX-LIUZHOU</x:v>
+      </x:c>
+      <x:c r="C363" s="2" t="str">
+        <x:v>柳州地区</x:v>
+      </x:c>
+      <x:c r="D363" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E363" s="2" t="str">
+        <x:v>广西壮族自治区</x:v>
+      </x:c>
+      <x:c r="F363" s="2" t="str">
+        <x:v>广西</x:v>
+      </x:c>
+      <x:c r="G363" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H363" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I363" s="2" t="str">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="J363" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K363" s="2" t="str">
+        <x:v>reviewed_county_composition</x:v>
+      </x:c>
+      <x:c r="L363" s="2" t="str">
+        <x:v>1987-2001 柳州地区</x:v>
+      </x:c>
+      <x:c r="M363" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N363" s="2" t="str">
+        <x:v>撤销后主要分为来宾市并将四县划归柳州市</x:v>
+      </x:c>
+      <x:c r="O363" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/柳州地区</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" ht="20" customHeight="1">
+      <x:c r="A364" s="2" t="str">
+        <x:v>CNUR-000363</x:v>
+      </x:c>
+      <x:c r="B364" s="2" t="str">
+        <x:v>HIST-GX-WUZHOU</x:v>
+      </x:c>
+      <x:c r="C364" s="2" t="str">
+        <x:v>梧州地区</x:v>
+      </x:c>
+      <x:c r="D364" s="2" t="str">
+        <x:v>historical_entity</x:v>
+      </x:c>
+      <x:c r="E364" s="2" t="str">
+        <x:v>广西壮族自治区</x:v>
+      </x:c>
+      <x:c r="F364" s="2" t="str">
+        <x:v>广西</x:v>
+      </x:c>
+      <x:c r="G364" s="2" t="str">
+        <x:v>abolished_prefecture</x:v>
+      </x:c>
+      <x:c r="H364" s="2" t="str">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="I364" s="2" t="str">
+        <x:v>1996</x:v>
+      </x:c>
+      <x:c r="J364" s="2" t="str">
+        <x:v>abolished</x:v>
+      </x:c>
+      <x:c r="K364" s="2" t="str">
+        <x:v>reviewed_county_composition</x:v>
+      </x:c>
+      <x:c r="L364" s="2" t="str">
+        <x:v>1987-1996 梧州地区</x:v>
+      </x:c>
+      <x:c r="M364" s="2" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N364" s="2" t="str">
+        <x:v>更名贺州地区时四县留归贺州、三县市划归既有梧州市</x:v>
+      </x:c>
+      <x:c r="O364" s="2" t="str">
+        <x:v>https://zh.wikipedia.org/wiki/1997年中华人民共和国县级以上行政区划变更列表</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01aebbe0ea2a43fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c4f683714d4525"/>
   </x:tableParts>
 </x:worksheet>
 </file>